--- a/Class_Gear_and_Gem_Database.xlsx
+++ b/Class_Gear_and_Gem_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orien\Desktop\mistfall calc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FE15EF-CBC9-47C8-88BB-74F7729335DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBAB0F1-93DD-4806-A416-0031FA731D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="315" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gear Database" sheetId="1" r:id="rId1"/>
@@ -1838,13 +1838,12 @@
   <dimension ref="A1:O1567"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.28515625" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="8" width="23" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9417,7 +9416,7 @@
         <v>13</v>
       </c>
       <c r="E295" s="22" t="s">
-        <v>15</v>
+        <v>262</v>
       </c>
       <c r="F295" s="22" t="s">
         <v>15</v>
@@ -9443,7 +9442,7 @@
         <v>13</v>
       </c>
       <c r="E296" s="22" t="s">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="F296" s="22" t="s">
         <v>15</v>
@@ -9469,7 +9468,7 @@
         <v>13</v>
       </c>
       <c r="E297" s="22" t="s">
-        <v>15</v>
+        <v>318</v>
       </c>
       <c r="F297" s="22" t="s">
         <v>15</v>
@@ -9495,7 +9494,7 @@
         <v>13</v>
       </c>
       <c r="E298" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F298" s="22" t="s">
         <v>15</v>
@@ -9521,7 +9520,7 @@
         <v>13</v>
       </c>
       <c r="E299" s="22" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="F299" s="22" t="s">
         <v>15</v>
@@ -9547,7 +9546,7 @@
         <v>13</v>
       </c>
       <c r="E300" s="22" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="F300" s="22" t="s">
         <v>15</v>
@@ -9573,7 +9572,7 @@
         <v>13</v>
       </c>
       <c r="E301" s="22" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="F301" s="22" t="s">
         <v>15</v>
@@ -9590,19 +9589,19 @@
         <v>61</v>
       </c>
       <c r="B302" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C302" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D302" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E302" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F302" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G302" s="22" t="s">
         <v>15</v>
@@ -9616,19 +9615,19 @@
         <v>61</v>
       </c>
       <c r="B303" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D303" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E303" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F303" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G303" s="22" t="s">
         <v>15</v>
@@ -9651,10 +9650,10 @@
         <v>25</v>
       </c>
       <c r="E304" s="22" t="s">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="F304" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G304" s="22" t="s">
         <v>15</v>
@@ -9677,10 +9676,10 @@
         <v>25</v>
       </c>
       <c r="E305" s="22" t="s">
-        <v>15</v>
+        <v>262</v>
       </c>
       <c r="F305" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G305" s="22" t="s">
         <v>15</v>
@@ -9703,10 +9702,10 @@
         <v>25</v>
       </c>
       <c r="E306" s="22" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="F306" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G306" s="22" t="s">
         <v>15</v>
@@ -9729,10 +9728,10 @@
         <v>25</v>
       </c>
       <c r="E307" s="22" t="s">
-        <v>15</v>
+        <v>318</v>
       </c>
       <c r="F307" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G307" s="22" t="s">
         <v>15</v>
@@ -9755,10 +9754,10 @@
         <v>25</v>
       </c>
       <c r="E308" s="22" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="F308" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G308" s="22" t="s">
         <v>15</v>
@@ -9781,10 +9780,10 @@
         <v>25</v>
       </c>
       <c r="E309" s="22" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="F309" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G309" s="22" t="s">
         <v>15</v>
@@ -9807,10 +9806,10 @@
         <v>25</v>
       </c>
       <c r="E310" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F310" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G310" s="22" t="s">
         <v>15</v>
@@ -9824,22 +9823,22 @@
         <v>61</v>
       </c>
       <c r="B311" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C311" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D311" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E311" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F311" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G311" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H311" s="22" t="s">
         <v>15</v>
@@ -9850,22 +9849,22 @@
         <v>61</v>
       </c>
       <c r="B312" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C312" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D312" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E312" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F312" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G312" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H312" s="22" t="s">
         <v>15</v>
@@ -9885,10 +9884,10 @@
         <v>28</v>
       </c>
       <c r="E313" s="22" t="s">
-        <v>15</v>
+        <v>262</v>
       </c>
       <c r="F313" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G313" s="22" t="s">
         <v>15</v>
@@ -9911,10 +9910,10 @@
         <v>28</v>
       </c>
       <c r="E314" s="22" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="F314" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G314" s="22" t="s">
         <v>15</v>
@@ -9937,10 +9936,10 @@
         <v>28</v>
       </c>
       <c r="E315" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F315" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G315" s="22" t="s">
         <v>15</v>
@@ -9963,10 +9962,10 @@
         <v>28</v>
       </c>
       <c r="E316" s="22" t="s">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="F316" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G316" s="22" t="s">
         <v>15</v>
@@ -9989,10 +9988,10 @@
         <v>28</v>
       </c>
       <c r="E317" s="22" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="F317" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G317" s="22" t="s">
         <v>15</v>
@@ -10015,10 +10014,10 @@
         <v>28</v>
       </c>
       <c r="E318" s="22" t="s">
-        <v>15</v>
+        <v>318</v>
       </c>
       <c r="F318" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G318" s="22" t="s">
         <v>15</v>
@@ -10041,10 +10040,10 @@
         <v>28</v>
       </c>
       <c r="E319" s="22" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="F319" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G319" s="22" t="s">
         <v>15</v>
@@ -10067,13 +10066,13 @@
         <v>30</v>
       </c>
       <c r="E320" s="22" t="s">
-        <v>15</v>
+        <v>262</v>
       </c>
       <c r="F320" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G320" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H320" s="22" t="s">
         <v>15</v>
@@ -10093,13 +10092,13 @@
         <v>30</v>
       </c>
       <c r="E321" s="22" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="F321" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G321" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H321" s="22" t="s">
         <v>15</v>
@@ -10119,13 +10118,13 @@
         <v>30</v>
       </c>
       <c r="E322" s="22" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="F322" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G322" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H322" s="22" t="s">
         <v>15</v>
@@ -10145,13 +10144,13 @@
         <v>30</v>
       </c>
       <c r="E323" s="22" t="s">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="F323" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G323" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H323" s="22" t="s">
         <v>15</v>
@@ -10171,13 +10170,13 @@
         <v>30</v>
       </c>
       <c r="E324" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F324" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G324" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H324" s="22" t="s">
         <v>15</v>
@@ -10197,67 +10196,67 @@
         <v>30</v>
       </c>
       <c r="E325" s="22" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="F325" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G325" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H325" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A326" s="4" t="s">
+      <c r="A326" s="10" t="s">
         <v>61</v>
       </c>
       <c r="B326" t="s">
         <v>69</v>
       </c>
-      <c r="C326" s="4" t="s">
+      <c r="C326" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D326" s="20" t="s">
+      <c r="D326" s="35" t="s">
         <v>30</v>
       </c>
       <c r="E326" s="22" t="s">
-        <v>15</v>
+        <v>318</v>
       </c>
       <c r="F326" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G326" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H326" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A327" s="4" t="s">
+      <c r="A327" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B327" t="s">
+      <c r="B327" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="C327" s="4" t="s">
+      <c r="C327" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D327" s="20" t="s">
+      <c r="D327" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="E327" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F327" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G327" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H327" s="22" t="s">
+      <c r="E327" s="29" t="s">
+        <v>286</v>
+      </c>
+      <c r="F327" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G327" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H327" s="29" t="s">
         <v>15</v>
       </c>
     </row>
@@ -10265,7 +10264,7 @@
       <c r="A328" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B328" t="s">
+      <c r="B328" s="17" t="s">
         <v>70</v>
       </c>
       <c r="C328" s="4" t="s">
@@ -10275,7 +10274,7 @@
         <v>13</v>
       </c>
       <c r="E328" s="22" t="s">
-        <v>15</v>
+        <v>340</v>
       </c>
       <c r="F328" s="22" t="s">
         <v>15</v>
@@ -10291,7 +10290,7 @@
       <c r="A329" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B329" t="s">
+      <c r="B329" s="17" t="s">
         <v>70</v>
       </c>
       <c r="C329" s="4" t="s">
@@ -10301,7 +10300,7 @@
         <v>13</v>
       </c>
       <c r="E329" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F329" s="22" t="s">
         <v>15</v>
@@ -10317,7 +10316,7 @@
       <c r="A330" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B330" t="s">
+      <c r="B330" s="17" t="s">
         <v>70</v>
       </c>
       <c r="C330" s="4" t="s">
@@ -10327,7 +10326,7 @@
         <v>13</v>
       </c>
       <c r="E330" s="22" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="F330" s="22" t="s">
         <v>15</v>
@@ -10343,7 +10342,7 @@
       <c r="A331" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B331" t="s">
+      <c r="B331" s="17" t="s">
         <v>70</v>
       </c>
       <c r="C331" s="4" t="s">
@@ -10353,7 +10352,7 @@
         <v>13</v>
       </c>
       <c r="E331" s="22" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="F331" s="22" t="s">
         <v>15</v>
@@ -10369,7 +10368,7 @@
       <c r="A332" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B332" t="s">
+      <c r="B332" s="17" t="s">
         <v>70</v>
       </c>
       <c r="C332" s="4" t="s">
@@ -10379,7 +10378,7 @@
         <v>13</v>
       </c>
       <c r="E332" s="22" t="s">
-        <v>15</v>
+        <v>262</v>
       </c>
       <c r="F332" s="22" t="s">
         <v>15</v>
@@ -10395,7 +10394,7 @@
       <c r="A333" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B333" t="s">
+      <c r="B333" s="17" t="s">
         <v>70</v>
       </c>
       <c r="C333" s="4" t="s">
@@ -10405,7 +10404,7 @@
         <v>13</v>
       </c>
       <c r="E333" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F333" s="22" t="s">
         <v>15</v>
@@ -10421,7 +10420,7 @@
       <c r="A334" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B334" t="s">
+      <c r="B334" s="17" t="s">
         <v>70</v>
       </c>
       <c r="C334" s="4" t="s">
@@ -10434,7 +10433,7 @@
         <v>15</v>
       </c>
       <c r="F334" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G334" s="22" t="s">
         <v>15</v>
@@ -10447,7 +10446,7 @@
       <c r="A335" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B335" t="s">
+      <c r="B335" s="17" t="s">
         <v>70</v>
       </c>
       <c r="C335" s="4" t="s">
@@ -10460,7 +10459,7 @@
         <v>15</v>
       </c>
       <c r="F335" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G335" s="22" t="s">
         <v>15</v>
@@ -10473,7 +10472,7 @@
       <c r="A336" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B336" t="s">
+      <c r="B336" s="17" t="s">
         <v>71</v>
       </c>
       <c r="C336" s="4" t="s">
@@ -10483,10 +10482,10 @@
         <v>25</v>
       </c>
       <c r="E336" s="22" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="F336" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G336" s="22" t="s">
         <v>15</v>
@@ -10499,7 +10498,7 @@
       <c r="A337" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B337" t="s">
+      <c r="B337" s="17" t="s">
         <v>71</v>
       </c>
       <c r="C337" s="4" t="s">
@@ -10509,10 +10508,10 @@
         <v>25</v>
       </c>
       <c r="E337" s="22" t="s">
-        <v>15</v>
+        <v>286</v>
       </c>
       <c r="F337" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G337" s="22" t="s">
         <v>15</v>
@@ -10525,7 +10524,7 @@
       <c r="A338" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B338" t="s">
+      <c r="B338" s="17" t="s">
         <v>71</v>
       </c>
       <c r="C338" s="4" t="s">
@@ -10535,10 +10534,10 @@
         <v>25</v>
       </c>
       <c r="E338" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F338" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G338" s="22" t="s">
         <v>15</v>
@@ -10551,7 +10550,7 @@
       <c r="A339" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B339" t="s">
+      <c r="B339" s="17" t="s">
         <v>71</v>
       </c>
       <c r="C339" s="4" t="s">
@@ -10561,10 +10560,10 @@
         <v>25</v>
       </c>
       <c r="E339" s="22" t="s">
-        <v>15</v>
+        <v>340</v>
       </c>
       <c r="F339" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G339" s="22" t="s">
         <v>15</v>
@@ -10577,7 +10576,7 @@
       <c r="A340" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B340" t="s">
+      <c r="B340" s="17" t="s">
         <v>71</v>
       </c>
       <c r="C340" s="4" t="s">
@@ -10587,10 +10586,10 @@
         <v>25</v>
       </c>
       <c r="E340" s="22" t="s">
-        <v>15</v>
+        <v>262</v>
       </c>
       <c r="F340" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G340" s="22" t="s">
         <v>15</v>
@@ -10603,7 +10602,7 @@
       <c r="A341" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B341" t="s">
+      <c r="B341" s="17" t="s">
         <v>71</v>
       </c>
       <c r="C341" s="4" t="s">
@@ -10613,10 +10612,10 @@
         <v>25</v>
       </c>
       <c r="E341" s="22" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="F341" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G341" s="22" t="s">
         <v>15</v>
@@ -10629,7 +10628,7 @@
       <c r="A342" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B342" t="s">
+      <c r="B342" s="17" t="s">
         <v>71</v>
       </c>
       <c r="C342" s="4" t="s">
@@ -10639,10 +10638,10 @@
         <v>25</v>
       </c>
       <c r="E342" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F342" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G342" s="22" t="s">
         <v>15</v>
@@ -10655,7 +10654,7 @@
       <c r="A343" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B343" t="s">
+      <c r="B343" s="17" t="s">
         <v>71</v>
       </c>
       <c r="C343" s="4" t="s">
@@ -10668,10 +10667,10 @@
         <v>15</v>
       </c>
       <c r="F343" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G343" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H343" s="22" t="s">
         <v>15</v>
@@ -10681,7 +10680,7 @@
       <c r="A344" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B344" t="s">
+      <c r="B344" s="17" t="s">
         <v>71</v>
       </c>
       <c r="C344" s="4" t="s">
@@ -10694,10 +10693,10 @@
         <v>15</v>
       </c>
       <c r="F344" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G344" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H344" s="22" t="s">
         <v>15</v>
@@ -10707,7 +10706,7 @@
       <c r="A345" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B345" t="s">
+      <c r="B345" s="17" t="s">
         <v>72</v>
       </c>
       <c r="C345" s="4" t="s">
@@ -10717,10 +10716,10 @@
         <v>28</v>
       </c>
       <c r="E345" s="22" t="s">
-        <v>15</v>
+        <v>340</v>
       </c>
       <c r="F345" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G345" s="22" t="s">
         <v>15</v>
@@ -10733,7 +10732,7 @@
       <c r="A346" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B346" t="s">
+      <c r="B346" s="17" t="s">
         <v>72</v>
       </c>
       <c r="C346" s="4" t="s">
@@ -10743,10 +10742,10 @@
         <v>28</v>
       </c>
       <c r="E346" s="22" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="F346" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G346" s="22" t="s">
         <v>15</v>
@@ -10759,7 +10758,7 @@
       <c r="A347" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B347" t="s">
+      <c r="B347" s="17" t="s">
         <v>72</v>
       </c>
       <c r="C347" s="4" t="s">
@@ -10769,10 +10768,10 @@
         <v>28</v>
       </c>
       <c r="E347" s="22" t="s">
-        <v>15</v>
+        <v>286</v>
       </c>
       <c r="F347" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G347" s="22" t="s">
         <v>15</v>
@@ -10785,7 +10784,7 @@
       <c r="A348" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B348" t="s">
+      <c r="B348" s="17" t="s">
         <v>72</v>
       </c>
       <c r="C348" s="4" t="s">
@@ -10795,10 +10794,10 @@
         <v>28</v>
       </c>
       <c r="E348" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F348" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G348" s="22" t="s">
         <v>15</v>
@@ -10811,7 +10810,7 @@
       <c r="A349" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B349" t="s">
+      <c r="B349" s="17" t="s">
         <v>72</v>
       </c>
       <c r="C349" s="4" t="s">
@@ -10821,10 +10820,10 @@
         <v>28</v>
       </c>
       <c r="E349" s="22" t="s">
-        <v>15</v>
+        <v>262</v>
       </c>
       <c r="F349" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G349" s="22" t="s">
         <v>15</v>
@@ -10837,7 +10836,7 @@
       <c r="A350" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B350" t="s">
+      <c r="B350" s="17" t="s">
         <v>72</v>
       </c>
       <c r="C350" s="4" t="s">
@@ -10847,10 +10846,10 @@
         <v>28</v>
       </c>
       <c r="E350" s="22" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="F350" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G350" s="22" t="s">
         <v>15</v>
@@ -10863,7 +10862,7 @@
       <c r="A351" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B351" t="s">
+      <c r="B351" s="17" t="s">
         <v>72</v>
       </c>
       <c r="C351" s="4" t="s">
@@ -10873,10 +10872,10 @@
         <v>28</v>
       </c>
       <c r="E351" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F351" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G351" s="22" t="s">
         <v>15</v>
@@ -10889,7 +10888,7 @@
       <c r="A352" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B352" t="s">
+      <c r="B352" s="17" t="s">
         <v>72</v>
       </c>
       <c r="C352" s="4" t="s">
@@ -10902,10 +10901,10 @@
         <v>15</v>
       </c>
       <c r="F352" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G352" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H352" s="22" t="s">
         <v>15</v>
@@ -10915,7 +10914,7 @@
       <c r="A353" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B353" t="s">
+      <c r="B353" s="17" t="s">
         <v>72</v>
       </c>
       <c r="C353" s="4" t="s">
@@ -10928,10 +10927,10 @@
         <v>15</v>
       </c>
       <c r="F353" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G353" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H353" s="22" t="s">
         <v>15</v>
@@ -10941,7 +10940,7 @@
       <c r="A354" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B354" t="s">
+      <c r="B354" s="17" t="s">
         <v>73</v>
       </c>
       <c r="C354" s="4" t="s">
@@ -10951,13 +10950,13 @@
         <v>30</v>
       </c>
       <c r="E354" s="22" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="F354" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G354" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H354" s="22" t="s">
         <v>15</v>
@@ -10967,7 +10966,7 @@
       <c r="A355" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B355" t="s">
+      <c r="B355" s="17" t="s">
         <v>73</v>
       </c>
       <c r="C355" s="4" t="s">
@@ -10977,13 +10976,13 @@
         <v>30</v>
       </c>
       <c r="E355" s="22" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="F355" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G355" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H355" s="22" t="s">
         <v>15</v>
@@ -10993,7 +10992,7 @@
       <c r="A356" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B356" t="s">
+      <c r="B356" s="17" t="s">
         <v>73</v>
       </c>
       <c r="C356" s="4" t="s">
@@ -11003,13 +11002,13 @@
         <v>30</v>
       </c>
       <c r="E356" s="22" t="s">
-        <v>15</v>
+        <v>340</v>
       </c>
       <c r="F356" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G356" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H356" s="22" t="s">
         <v>15</v>
@@ -11019,7 +11018,7 @@
       <c r="A357" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B357" t="s">
+      <c r="B357" s="17" t="s">
         <v>73</v>
       </c>
       <c r="C357" s="4" t="s">
@@ -11029,13 +11028,13 @@
         <v>30</v>
       </c>
       <c r="E357" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F357" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G357" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H357" s="22" t="s">
         <v>15</v>
@@ -11045,7 +11044,7 @@
       <c r="A358" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B358" t="s">
+      <c r="B358" s="17" t="s">
         <v>73</v>
       </c>
       <c r="C358" s="4" t="s">
@@ -11055,13 +11054,13 @@
         <v>30</v>
       </c>
       <c r="E358" s="22" t="s">
-        <v>15</v>
+        <v>262</v>
       </c>
       <c r="F358" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G358" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H358" s="22" t="s">
         <v>15</v>
@@ -11071,7 +11070,7 @@
       <c r="A359" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B359" t="s">
+      <c r="B359" s="17" t="s">
         <v>73</v>
       </c>
       <c r="C359" s="4" t="s">
@@ -11081,13 +11080,13 @@
         <v>30</v>
       </c>
       <c r="E359" s="22" t="s">
-        <v>15</v>
+        <v>286</v>
       </c>
       <c r="F359" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G359" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H359" s="22" t="s">
         <v>15</v>
@@ -11097,7 +11096,7 @@
       <c r="A360" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B360" t="s">
+      <c r="B360" s="17" t="s">
         <v>73</v>
       </c>
       <c r="C360" s="4" t="s">
@@ -11107,13 +11106,13 @@
         <v>30</v>
       </c>
       <c r="E360" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F360" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G360" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H360" s="22" t="s">
         <v>15</v>
@@ -11123,77 +11122,77 @@
       <c r="A361" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B361" t="s">
+      <c r="B361" s="17" t="s">
         <v>74</v>
       </c>
       <c r="C361" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D361" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E361" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="F361" s="22" t="s">
+        <v>372</v>
+      </c>
+      <c r="G361" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="H361" s="22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A362" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B362" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C362" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D362" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E362" s="32" t="s">
+        <v>357</v>
+      </c>
+      <c r="F362" s="32" t="s">
+        <v>370</v>
+      </c>
+      <c r="G362" s="32" t="s">
+        <v>368</v>
+      </c>
+      <c r="H362" s="32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A363" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B363" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C363" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D361" s="20" t="s">
+      <c r="D363" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="E361" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F361" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G361" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H361" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A362" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B362" t="s">
-        <v>74</v>
-      </c>
-      <c r="C362" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D362" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E362" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F362" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G362" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H362" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A363" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B363" t="s">
-        <v>74</v>
-      </c>
-      <c r="C363" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D363" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E363" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F363" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G363" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H363" s="22" t="s">
+      <c r="E363" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F363" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G363" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H363" s="29" t="s">
         <v>15</v>
       </c>
     </row>
@@ -11201,7 +11200,7 @@
       <c r="A364" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B364" t="s">
+      <c r="B364" s="17" t="s">
         <v>74</v>
       </c>
       <c r="C364" s="4" t="s">
@@ -11211,7 +11210,7 @@
         <v>13</v>
       </c>
       <c r="E364" s="22" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="F364" s="22" t="s">
         <v>15</v>
@@ -11227,7 +11226,7 @@
       <c r="A365" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B365" t="s">
+      <c r="B365" s="17" t="s">
         <v>74</v>
       </c>
       <c r="C365" s="4" t="s">
@@ -11237,7 +11236,7 @@
         <v>13</v>
       </c>
       <c r="E365" s="22" t="s">
-        <v>15</v>
+        <v>343</v>
       </c>
       <c r="F365" s="22" t="s">
         <v>15</v>
@@ -11253,7 +11252,7 @@
       <c r="A366" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B366" t="s">
+      <c r="B366" s="17" t="s">
         <v>74</v>
       </c>
       <c r="C366" s="4" t="s">
@@ -11263,7 +11262,7 @@
         <v>13</v>
       </c>
       <c r="E366" s="22" t="s">
-        <v>15</v>
+        <v>318</v>
       </c>
       <c r="F366" s="22" t="s">
         <v>15</v>
@@ -11279,7 +11278,7 @@
       <c r="A367" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B367" t="s">
+      <c r="B367" s="17" t="s">
         <v>74</v>
       </c>
       <c r="C367" s="4" t="s">
@@ -11289,7 +11288,7 @@
         <v>13</v>
       </c>
       <c r="E367" s="22" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="F367" s="22" t="s">
         <v>15</v>
@@ -11305,7 +11304,7 @@
       <c r="A368" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B368" t="s">
+      <c r="B368" s="17" t="s">
         <v>74</v>
       </c>
       <c r="C368" s="4" t="s">
@@ -11315,7 +11314,7 @@
         <v>13</v>
       </c>
       <c r="E368" s="22" t="s">
-        <v>15</v>
+        <v>340</v>
       </c>
       <c r="F368" s="22" t="s">
         <v>15</v>
@@ -11331,7 +11330,7 @@
       <c r="A369" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B369" t="s">
+      <c r="B369" s="17" t="s">
         <v>74</v>
       </c>
       <c r="C369" s="4" t="s">
@@ -11341,7 +11340,7 @@
         <v>13</v>
       </c>
       <c r="E369" s="22" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="F369" s="22" t="s">
         <v>15</v>
@@ -11357,20 +11356,20 @@
       <c r="A370" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B370" t="s">
-        <v>76</v>
+      <c r="B370" s="17" t="s">
+        <v>74</v>
       </c>
       <c r="C370" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D370" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E370" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F370" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G370" s="22" t="s">
         <v>15</v>
@@ -11383,20 +11382,20 @@
       <c r="A371" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B371" t="s">
-        <v>76</v>
+      <c r="B371" s="17" t="s">
+        <v>74</v>
       </c>
       <c r="C371" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D371" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E371" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F371" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G371" s="22" t="s">
         <v>15</v>
@@ -11409,7 +11408,7 @@
       <c r="A372" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B372" t="s">
+      <c r="B372" s="17" t="s">
         <v>76</v>
       </c>
       <c r="C372" s="4" t="s">
@@ -11419,10 +11418,10 @@
         <v>25</v>
       </c>
       <c r="E372" s="22" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="F372" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G372" s="22" t="s">
         <v>15</v>
@@ -11435,7 +11434,7 @@
       <c r="A373" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B373" t="s">
+      <c r="B373" s="17" t="s">
         <v>76</v>
       </c>
       <c r="C373" s="4" t="s">
@@ -11445,10 +11444,10 @@
         <v>25</v>
       </c>
       <c r="E373" s="22" t="s">
-        <v>15</v>
+        <v>340</v>
       </c>
       <c r="F373" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G373" s="22" t="s">
         <v>15</v>
@@ -11461,7 +11460,7 @@
       <c r="A374" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B374" t="s">
+      <c r="B374" s="17" t="s">
         <v>76</v>
       </c>
       <c r="C374" s="4" t="s">
@@ -11471,10 +11470,10 @@
         <v>25</v>
       </c>
       <c r="E374" s="22" t="s">
-        <v>15</v>
+        <v>343</v>
       </c>
       <c r="F374" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G374" s="22" t="s">
         <v>15</v>
@@ -11487,7 +11486,7 @@
       <c r="A375" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B375" t="s">
+      <c r="B375" s="17" t="s">
         <v>76</v>
       </c>
       <c r="C375" s="4" t="s">
@@ -11497,10 +11496,10 @@
         <v>25</v>
       </c>
       <c r="E375" s="22" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="F375" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G375" s="22" t="s">
         <v>15</v>
@@ -11513,7 +11512,7 @@
       <c r="A376" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B376" t="s">
+      <c r="B376" s="17" t="s">
         <v>76</v>
       </c>
       <c r="C376" s="4" t="s">
@@ -11523,10 +11522,10 @@
         <v>25</v>
       </c>
       <c r="E376" s="22" t="s">
-        <v>15</v>
+        <v>318</v>
       </c>
       <c r="F376" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G376" s="22" t="s">
         <v>15</v>
@@ -11539,7 +11538,7 @@
       <c r="A377" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B377" t="s">
+      <c r="B377" s="17" t="s">
         <v>76</v>
       </c>
       <c r="C377" s="4" t="s">
@@ -11549,10 +11548,10 @@
         <v>25</v>
       </c>
       <c r="E377" s="22" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="F377" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G377" s="22" t="s">
         <v>15</v>
@@ -11565,7 +11564,7 @@
       <c r="A378" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B378" t="s">
+      <c r="B378" s="17" t="s">
         <v>76</v>
       </c>
       <c r="C378" s="4" t="s">
@@ -11575,10 +11574,10 @@
         <v>25</v>
       </c>
       <c r="E378" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F378" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G378" s="22" t="s">
         <v>15</v>
@@ -11591,23 +11590,23 @@
       <c r="A379" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B379" t="s">
-        <v>77</v>
+      <c r="B379" s="17" t="s">
+        <v>76</v>
       </c>
       <c r="C379" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D379" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E379" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F379" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G379" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H379" s="22" t="s">
         <v>15</v>
@@ -11617,23 +11616,23 @@
       <c r="A380" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B380" t="s">
-        <v>77</v>
+      <c r="B380" s="17" t="s">
+        <v>76</v>
       </c>
       <c r="C380" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D380" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E380" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F380" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G380" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H380" s="22" t="s">
         <v>15</v>
@@ -11643,7 +11642,7 @@
       <c r="A381" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B381" t="s">
+      <c r="B381" s="17" t="s">
         <v>77</v>
       </c>
       <c r="C381" s="4" t="s">
@@ -11653,10 +11652,10 @@
         <v>28</v>
       </c>
       <c r="E381" s="22" t="s">
-        <v>15</v>
+        <v>318</v>
       </c>
       <c r="F381" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G381" s="22" t="s">
         <v>15</v>
@@ -11669,7 +11668,7 @@
       <c r="A382" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B382" t="s">
+      <c r="B382" s="17" t="s">
         <v>77</v>
       </c>
       <c r="C382" s="4" t="s">
@@ -11679,10 +11678,10 @@
         <v>28</v>
       </c>
       <c r="E382" s="22" t="s">
-        <v>15</v>
+        <v>340</v>
       </c>
       <c r="F382" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G382" s="22" t="s">
         <v>15</v>
@@ -11695,7 +11694,7 @@
       <c r="A383" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B383" t="s">
+      <c r="B383" s="17" t="s">
         <v>77</v>
       </c>
       <c r="C383" s="4" t="s">
@@ -11705,10 +11704,10 @@
         <v>28</v>
       </c>
       <c r="E383" s="22" t="s">
-        <v>15</v>
+        <v>343</v>
       </c>
       <c r="F383" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G383" s="22" t="s">
         <v>15</v>
@@ -11721,7 +11720,7 @@
       <c r="A384" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B384" t="s">
+      <c r="B384" s="17" t="s">
         <v>77</v>
       </c>
       <c r="C384" s="4" t="s">
@@ -11731,10 +11730,10 @@
         <v>28</v>
       </c>
       <c r="E384" s="22" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="F384" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G384" s="22" t="s">
         <v>15</v>
@@ -11747,7 +11746,7 @@
       <c r="A385" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B385" t="s">
+      <c r="B385" s="17" t="s">
         <v>77</v>
       </c>
       <c r="C385" s="4" t="s">
@@ -11757,10 +11756,10 @@
         <v>28</v>
       </c>
       <c r="E385" s="22" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="F385" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G385" s="22" t="s">
         <v>15</v>
@@ -11773,7 +11772,7 @@
       <c r="A386" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B386" t="s">
+      <c r="B386" s="17" t="s">
         <v>77</v>
       </c>
       <c r="C386" s="4" t="s">
@@ -11783,10 +11782,10 @@
         <v>28</v>
       </c>
       <c r="E386" s="22" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="F386" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G386" s="22" t="s">
         <v>15</v>
@@ -11799,7 +11798,7 @@
       <c r="A387" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B387" t="s">
+      <c r="B387" s="17" t="s">
         <v>77</v>
       </c>
       <c r="C387" s="4" t="s">
@@ -11809,10 +11808,10 @@
         <v>28</v>
       </c>
       <c r="E387" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F387" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G387" s="22" t="s">
         <v>15</v>
@@ -11825,23 +11824,23 @@
       <c r="A388" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B388" t="s">
-        <v>78</v>
+      <c r="B388" s="17" t="s">
+        <v>77</v>
       </c>
       <c r="C388" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D388" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E388" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F388" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G388" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H388" s="22" t="s">
         <v>15</v>
@@ -11851,23 +11850,23 @@
       <c r="A389" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B389" t="s">
-        <v>78</v>
+      <c r="B389" s="17" t="s">
+        <v>77</v>
       </c>
       <c r="C389" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D389" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E389" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F389" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G389" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H389" s="22" t="s">
         <v>15</v>
@@ -11877,7 +11876,7 @@
       <c r="A390" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B390" t="s">
+      <c r="B390" s="17" t="s">
         <v>78</v>
       </c>
       <c r="C390" s="4" t="s">
@@ -11887,13 +11886,13 @@
         <v>30</v>
       </c>
       <c r="E390" s="22" t="s">
-        <v>15</v>
+        <v>343</v>
       </c>
       <c r="F390" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G390" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H390" s="22" t="s">
         <v>15</v>
@@ -11903,7 +11902,7 @@
       <c r="A391" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B391" t="s">
+      <c r="B391" s="17" t="s">
         <v>78</v>
       </c>
       <c r="C391" s="4" t="s">
@@ -11913,13 +11912,13 @@
         <v>30</v>
       </c>
       <c r="E391" s="22" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="F391" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G391" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H391" s="22" t="s">
         <v>15</v>
@@ -11929,7 +11928,7 @@
       <c r="A392" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B392" t="s">
+      <c r="B392" s="17" t="s">
         <v>78</v>
       </c>
       <c r="C392" s="4" t="s">
@@ -11939,13 +11938,13 @@
         <v>30</v>
       </c>
       <c r="E392" s="22" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="F392" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G392" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H392" s="22" t="s">
         <v>15</v>
@@ -11955,7 +11954,7 @@
       <c r="A393" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B393" t="s">
+      <c r="B393" s="17" t="s">
         <v>78</v>
       </c>
       <c r="C393" s="4" t="s">
@@ -11965,13 +11964,13 @@
         <v>30</v>
       </c>
       <c r="E393" s="22" t="s">
-        <v>15</v>
+        <v>340</v>
       </c>
       <c r="F393" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G393" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H393" s="22" t="s">
         <v>15</v>
@@ -11981,7 +11980,7 @@
       <c r="A394" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B394" t="s">
+      <c r="B394" s="17" t="s">
         <v>78</v>
       </c>
       <c r="C394" s="4" t="s">
@@ -11991,13 +11990,13 @@
         <v>30</v>
       </c>
       <c r="E394" s="22" t="s">
-        <v>15</v>
+        <v>318</v>
       </c>
       <c r="F394" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G394" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H394" s="22" t="s">
         <v>15</v>
@@ -12007,23 +12006,23 @@
       <c r="A395" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B395" t="s">
-        <v>79</v>
+      <c r="B395" s="17" t="s">
+        <v>78</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D395" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E395" s="22" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="F395" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G395" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H395" s="22" t="s">
         <v>15</v>
@@ -12033,23 +12032,23 @@
       <c r="A396" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B396" t="s">
-        <v>79</v>
+      <c r="B396" s="17" t="s">
+        <v>78</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D396" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E396" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F396" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G396" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H396" s="22" t="s">
         <v>15</v>
@@ -12059,69 +12058,69 @@
       <c r="A397" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B397" t="s">
-        <v>79</v>
+      <c r="B397" s="17" t="s">
+        <v>78</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D397" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E397" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F397" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G397" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H397" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A398" s="4" t="s">
+      <c r="A398" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B398" t="s">
-        <v>79</v>
-      </c>
-      <c r="C398" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D398" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E398" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F398" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G398" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H398" s="22" t="s">
-        <v>15</v>
+      <c r="B398" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C398" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D398" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E398" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F398" s="32" t="s">
+        <v>371</v>
+      </c>
+      <c r="G398" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="H398" s="32" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A399" s="4" t="s">
+      <c r="A399" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B399" t="s">
         <v>79</v>
       </c>
-      <c r="C399" s="4" t="s">
+      <c r="C399" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D399" s="20" t="s">
+      <c r="D399" s="19" t="s">
         <v>13</v>
       </c>
       <c r="E399" s="22" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F399" s="22" t="s">
         <v>15</v>
@@ -12147,7 +12146,7 @@
         <v>13</v>
       </c>
       <c r="E400" s="22" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="F400" s="22" t="s">
         <v>15</v>
@@ -12173,7 +12172,7 @@
         <v>13</v>
       </c>
       <c r="E401" s="22" t="s">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="F401" s="22" t="s">
         <v>15</v>
@@ -12199,7 +12198,7 @@
         <v>13</v>
       </c>
       <c r="E402" s="22" t="s">
-        <v>15</v>
+        <v>318</v>
       </c>
       <c r="F402" s="22" t="s">
         <v>15</v>
@@ -12225,7 +12224,7 @@
         <v>13</v>
       </c>
       <c r="E403" s="22" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="F403" s="22" t="s">
         <v>15</v>
@@ -12242,16 +12241,16 @@
         <v>61</v>
       </c>
       <c r="B404" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C404" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D404" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E404" s="22" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F404" s="22" t="s">
         <v>15</v>
@@ -12268,16 +12267,16 @@
         <v>61</v>
       </c>
       <c r="B405" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C405" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D405" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E405" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F405" s="22" t="s">
         <v>15</v>
@@ -12294,19 +12293,19 @@
         <v>61</v>
       </c>
       <c r="B406" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C406" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D406" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E406" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F406" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G406" s="22" t="s">
         <v>15</v>
@@ -12320,19 +12319,19 @@
         <v>61</v>
       </c>
       <c r="B407" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C407" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D407" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E407" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F407" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G407" s="22" t="s">
         <v>15</v>
@@ -12355,10 +12354,10 @@
         <v>25</v>
       </c>
       <c r="E408" s="22" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="F408" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G408" s="22" t="s">
         <v>15</v>
@@ -12381,10 +12380,10 @@
         <v>25</v>
       </c>
       <c r="E409" s="22" t="s">
-        <v>15</v>
+        <v>318</v>
       </c>
       <c r="F409" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G409" s="22" t="s">
         <v>15</v>
@@ -12407,10 +12406,10 @@
         <v>25</v>
       </c>
       <c r="E410" s="22" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="F410" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G410" s="22" t="s">
         <v>15</v>
@@ -12433,10 +12432,10 @@
         <v>25</v>
       </c>
       <c r="E411" s="22" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="F411" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G411" s="22" t="s">
         <v>15</v>
@@ -12459,10 +12458,10 @@
         <v>25</v>
       </c>
       <c r="E412" s="22" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F412" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G412" s="22" t="s">
         <v>15</v>
@@ -12476,19 +12475,19 @@
         <v>61</v>
       </c>
       <c r="B413" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C413" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D413" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E413" s="22" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F413" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G413" s="22" t="s">
         <v>15</v>
@@ -12502,19 +12501,19 @@
         <v>61</v>
       </c>
       <c r="B414" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C414" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D414" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E414" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F414" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G414" s="22" t="s">
         <v>15</v>
@@ -12528,22 +12527,22 @@
         <v>61</v>
       </c>
       <c r="B415" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C415" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D415" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E415" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F415" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G415" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H415" s="22" t="s">
         <v>15</v>
@@ -12554,22 +12553,22 @@
         <v>61</v>
       </c>
       <c r="B416" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C416" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D416" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E416" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F416" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G416" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H416" s="22" t="s">
         <v>15</v>
@@ -12589,10 +12588,10 @@
         <v>28</v>
       </c>
       <c r="E417" s="22" t="s">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="F417" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G417" s="22" t="s">
         <v>15</v>
@@ -12615,10 +12614,10 @@
         <v>28</v>
       </c>
       <c r="E418" s="22" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="F418" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G418" s="22" t="s">
         <v>15</v>
@@ -12641,10 +12640,10 @@
         <v>28</v>
       </c>
       <c r="E419" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F419" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G419" s="22" t="s">
         <v>15</v>
@@ -12667,10 +12666,10 @@
         <v>28</v>
       </c>
       <c r="E420" s="22" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F420" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G420" s="22" t="s">
         <v>15</v>
@@ -12693,10 +12692,10 @@
         <v>28</v>
       </c>
       <c r="E421" s="22" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="F421" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G421" s="22" t="s">
         <v>15</v>
@@ -12710,19 +12709,19 @@
         <v>61</v>
       </c>
       <c r="B422" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C422" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D422" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E422" s="22" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F422" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G422" s="22" t="s">
         <v>15</v>
@@ -12736,19 +12735,19 @@
         <v>61</v>
       </c>
       <c r="B423" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C423" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D423" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E423" s="22" t="s">
-        <v>15</v>
+        <v>318</v>
       </c>
       <c r="F423" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G423" s="22" t="s">
         <v>15</v>
@@ -12762,22 +12761,22 @@
         <v>61</v>
       </c>
       <c r="B424" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C424" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D424" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E424" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F424" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G424" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H424" s="22" t="s">
         <v>15</v>
@@ -12788,22 +12787,22 @@
         <v>61</v>
       </c>
       <c r="B425" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C425" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D425" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E425" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F425" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G425" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H425" s="22" t="s">
         <v>15</v>
@@ -12823,13 +12822,13 @@
         <v>30</v>
       </c>
       <c r="E426" s="22" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F426" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G426" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H426" s="22" t="s">
         <v>15</v>
@@ -12849,13 +12848,13 @@
         <v>30</v>
       </c>
       <c r="E427" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F427" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G427" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H427" s="22" t="s">
         <v>15</v>
@@ -12875,13 +12874,13 @@
         <v>30</v>
       </c>
       <c r="E428" s="22" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="F428" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G428" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H428" s="22" t="s">
         <v>15</v>
@@ -12892,22 +12891,22 @@
         <v>61</v>
       </c>
       <c r="B429" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D429" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E429" s="22" t="s">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="F429" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G429" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H429" s="22" t="s">
         <v>15</v>
@@ -12918,22 +12917,22 @@
         <v>61</v>
       </c>
       <c r="B430" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D430" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E430" s="22" t="s">
-        <v>15</v>
+        <v>318</v>
       </c>
       <c r="F430" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G430" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H430" s="22" t="s">
         <v>15</v>
@@ -12944,22 +12943,22 @@
         <v>61</v>
       </c>
       <c r="B431" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D431" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E431" s="22" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="F431" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G431" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H431" s="22" t="s">
         <v>15</v>
@@ -12970,22 +12969,22 @@
         <v>61</v>
       </c>
       <c r="B432" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D432" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E432" s="22" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F432" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G432" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H432" s="22" t="s">
         <v>15</v>
@@ -12996,76 +12995,76 @@
         <v>61</v>
       </c>
       <c r="B433" t="s">
+        <v>82</v>
+      </c>
+      <c r="C433" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D433" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E433" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F433" s="22" t="s">
+        <v>372</v>
+      </c>
+      <c r="G433" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H433" s="22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A434" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B434" t="s">
+        <v>82</v>
+      </c>
+      <c r="C434" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D434" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="E434" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F434" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="G434" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H434" s="22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A435" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B435" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="C433" s="4" t="s">
+      <c r="C435" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D433" s="20" t="s">
+      <c r="D435" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="E433" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F433" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G433" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H433" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A434" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B434" t="s">
-        <v>83</v>
-      </c>
-      <c r="C434" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D434" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E434" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F434" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G434" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H434" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A435" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B435" t="s">
-        <v>83</v>
-      </c>
-      <c r="C435" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D435" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E435" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F435" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G435" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H435" s="22" t="s">
+      <c r="E435" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="F435" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G435" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H435" s="29" t="s">
         <v>15</v>
       </c>
     </row>
@@ -13073,7 +13072,7 @@
       <c r="A436" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B436" t="s">
+      <c r="B436" s="17" t="s">
         <v>83</v>
       </c>
       <c r="C436" s="4" t="s">
@@ -13083,7 +13082,7 @@
         <v>13</v>
       </c>
       <c r="E436" s="22" t="s">
-        <v>15</v>
+        <v>254</v>
       </c>
       <c r="F436" s="22" t="s">
         <v>15</v>
@@ -13099,7 +13098,7 @@
       <c r="A437" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B437" t="s">
+      <c r="B437" s="17" t="s">
         <v>83</v>
       </c>
       <c r="C437" s="4" t="s">
@@ -13109,7 +13108,7 @@
         <v>13</v>
       </c>
       <c r="E437" s="22" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="F437" s="22" t="s">
         <v>15</v>
@@ -13125,17 +13124,17 @@
       <c r="A438" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B438" t="s">
-        <v>84</v>
+      <c r="B438" s="17" t="s">
+        <v>83</v>
       </c>
       <c r="C438" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D438" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E438" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F438" s="22" t="s">
         <v>15</v>
@@ -13151,17 +13150,17 @@
       <c r="A439" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B439" t="s">
-        <v>84</v>
+      <c r="B439" s="17" t="s">
+        <v>83</v>
       </c>
       <c r="C439" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D439" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E439" s="22" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F439" s="22" t="s">
         <v>15</v>
@@ -13177,17 +13176,17 @@
       <c r="A440" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B440" t="s">
-        <v>84</v>
+      <c r="B440" s="17" t="s">
+        <v>83</v>
       </c>
       <c r="C440" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D440" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E440" s="22" t="s">
-        <v>15</v>
+        <v>343</v>
       </c>
       <c r="F440" s="22" t="s">
         <v>15</v>
@@ -13203,17 +13202,17 @@
       <c r="A441" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B441" t="s">
-        <v>84</v>
+      <c r="B441" s="17" t="s">
+        <v>83</v>
       </c>
       <c r="C441" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D441" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E441" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F441" s="22" t="s">
         <v>15</v>
@@ -13229,20 +13228,20 @@
       <c r="A442" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B442" t="s">
-        <v>84</v>
+      <c r="B442" s="17" t="s">
+        <v>83</v>
       </c>
       <c r="C442" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D442" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E442" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F442" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G442" s="22" t="s">
         <v>15</v>
@@ -13255,20 +13254,20 @@
       <c r="A443" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B443" t="s">
-        <v>84</v>
+      <c r="B443" s="17" t="s">
+        <v>83</v>
       </c>
       <c r="C443" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D443" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E443" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F443" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G443" s="22" t="s">
         <v>15</v>
@@ -13281,7 +13280,7 @@
       <c r="A444" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B444" t="s">
+      <c r="B444" s="17" t="s">
         <v>84</v>
       </c>
       <c r="C444" s="4" t="s">
@@ -13291,10 +13290,10 @@
         <v>25</v>
       </c>
       <c r="E444" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F444" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G444" s="22" t="s">
         <v>15</v>
@@ -13307,7 +13306,7 @@
       <c r="A445" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B445" t="s">
+      <c r="B445" s="17" t="s">
         <v>84</v>
       </c>
       <c r="C445" s="4" t="s">
@@ -13317,10 +13316,10 @@
         <v>25</v>
       </c>
       <c r="E445" s="22" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F445" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G445" s="22" t="s">
         <v>15</v>
@@ -13333,7 +13332,7 @@
       <c r="A446" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B446" t="s">
+      <c r="B446" s="17" t="s">
         <v>84</v>
       </c>
       <c r="C446" s="4" t="s">
@@ -13343,10 +13342,10 @@
         <v>25</v>
       </c>
       <c r="E446" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F446" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G446" s="22" t="s">
         <v>15</v>
@@ -13359,20 +13358,20 @@
       <c r="A447" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B447" t="s">
-        <v>85</v>
+      <c r="B447" s="17" t="s">
+        <v>84</v>
       </c>
       <c r="C447" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D447" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E447" s="22" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="F447" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G447" s="22" t="s">
         <v>15</v>
@@ -13385,20 +13384,20 @@
       <c r="A448" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B448" t="s">
-        <v>85</v>
+      <c r="B448" s="17" t="s">
+        <v>84</v>
       </c>
       <c r="C448" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D448" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E448" s="22" t="s">
-        <v>15</v>
+        <v>254</v>
       </c>
       <c r="F448" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G448" s="22" t="s">
         <v>15</v>
@@ -13411,20 +13410,20 @@
       <c r="A449" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B449" t="s">
-        <v>85</v>
+      <c r="B449" s="17" t="s">
+        <v>84</v>
       </c>
       <c r="C449" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D449" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E449" s="22" t="s">
-        <v>15</v>
+        <v>343</v>
       </c>
       <c r="F449" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G449" s="22" t="s">
         <v>15</v>
@@ -13437,20 +13436,20 @@
       <c r="A450" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B450" t="s">
-        <v>85</v>
+      <c r="B450" s="17" t="s">
+        <v>84</v>
       </c>
       <c r="C450" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D450" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E450" s="22" t="s">
-        <v>15</v>
+        <v>340</v>
       </c>
       <c r="F450" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G450" s="22" t="s">
         <v>15</v>
@@ -13463,23 +13462,23 @@
       <c r="A451" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B451" t="s">
-        <v>85</v>
+      <c r="B451" s="17" t="s">
+        <v>84</v>
       </c>
       <c r="C451" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D451" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E451" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F451" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G451" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H451" s="22" t="s">
         <v>15</v>
@@ -13489,23 +13488,23 @@
       <c r="A452" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B452" t="s">
-        <v>85</v>
+      <c r="B452" s="17" t="s">
+        <v>84</v>
       </c>
       <c r="C452" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D452" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E452" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F452" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G452" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H452" s="22" t="s">
         <v>15</v>
@@ -13515,7 +13514,7 @@
       <c r="A453" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B453" t="s">
+      <c r="B453" s="17" t="s">
         <v>85</v>
       </c>
       <c r="C453" s="4" t="s">
@@ -13525,10 +13524,10 @@
         <v>28</v>
       </c>
       <c r="E453" s="22" t="s">
-        <v>15</v>
+        <v>254</v>
       </c>
       <c r="F453" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G453" s="22" t="s">
         <v>15</v>
@@ -13541,7 +13540,7 @@
       <c r="A454" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B454" t="s">
+      <c r="B454" s="17" t="s">
         <v>85</v>
       </c>
       <c r="C454" s="4" t="s">
@@ -13551,10 +13550,10 @@
         <v>28</v>
       </c>
       <c r="E454" s="22" t="s">
-        <v>15</v>
+        <v>340</v>
       </c>
       <c r="F454" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G454" s="22" t="s">
         <v>15</v>
@@ -13567,7 +13566,7 @@
       <c r="A455" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B455" t="s">
+      <c r="B455" s="17" t="s">
         <v>85</v>
       </c>
       <c r="C455" s="4" t="s">
@@ -13577,10 +13576,10 @@
         <v>28</v>
       </c>
       <c r="E455" s="22" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="F455" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G455" s="22" t="s">
         <v>15</v>
@@ -13593,20 +13592,20 @@
       <c r="A456" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B456" t="s">
-        <v>86</v>
+      <c r="B456" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="C456" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D456" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E456" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F456" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G456" s="22" t="s">
         <v>15</v>
@@ -13619,20 +13618,20 @@
       <c r="A457" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B457" t="s">
-        <v>86</v>
+      <c r="B457" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="C457" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D457" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E457" s="22" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F457" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G457" s="22" t="s">
         <v>15</v>
@@ -13645,20 +13644,20 @@
       <c r="A458" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B458" t="s">
-        <v>86</v>
+      <c r="B458" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="C458" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D458" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E458" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F458" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G458" s="22" t="s">
         <v>15</v>
@@ -13671,20 +13670,20 @@
       <c r="A459" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B459" t="s">
-        <v>86</v>
+      <c r="B459" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="C459" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D459" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E459" s="22" t="s">
-        <v>15</v>
+        <v>343</v>
       </c>
       <c r="F459" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G459" s="22" t="s">
         <v>15</v>
@@ -13697,23 +13696,23 @@
       <c r="A460" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B460" t="s">
-        <v>86</v>
+      <c r="B460" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="C460" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D460" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E460" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F460" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G460" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H460" s="22" t="s">
         <v>15</v>
@@ -13723,23 +13722,23 @@
       <c r="A461" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B461" t="s">
-        <v>86</v>
+      <c r="B461" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="C461" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D461" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E461" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F461" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G461" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H461" s="22" t="s">
         <v>15</v>
@@ -13749,7 +13748,7 @@
       <c r="A462" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B462" t="s">
+      <c r="B462" s="17" t="s">
         <v>86</v>
       </c>
       <c r="C462" s="4" t="s">
@@ -13759,13 +13758,13 @@
         <v>30</v>
       </c>
       <c r="E462" s="22" t="s">
-        <v>15</v>
+        <v>254</v>
       </c>
       <c r="F462" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G462" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H462" s="22" t="s">
         <v>15</v>
@@ -13773,25 +13772,25 @@
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B463" t="s">
-        <v>88</v>
+        <v>61</v>
+      </c>
+      <c r="B463" s="17" t="s">
+        <v>86</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="D463" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E463" s="22" t="s">
-        <v>15</v>
+        <v>340</v>
       </c>
       <c r="F463" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G463" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H463" s="22" t="s">
         <v>15</v>
@@ -13799,25 +13798,25 @@
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B464" t="s">
-        <v>88</v>
+        <v>61</v>
+      </c>
+      <c r="B464" s="17" t="s">
+        <v>86</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="D464" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E464" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F464" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G464" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H464" s="22" t="s">
         <v>15</v>
@@ -13825,25 +13824,25 @@
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B465" t="s">
-        <v>88</v>
+        <v>61</v>
+      </c>
+      <c r="B465" s="17" t="s">
+        <v>86</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="D465" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E465" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F465" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G465" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H465" s="22" t="s">
         <v>15</v>
@@ -13851,25 +13850,25 @@
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B466" t="s">
-        <v>88</v>
+        <v>61</v>
+      </c>
+      <c r="B466" s="17" t="s">
+        <v>86</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="D466" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E466" s="22" t="s">
-        <v>15</v>
+        <v>343</v>
       </c>
       <c r="F466" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G466" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H466" s="22" t="s">
         <v>15</v>
@@ -13877,25 +13876,25 @@
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B467" t="s">
-        <v>88</v>
+        <v>61</v>
+      </c>
+      <c r="B467" s="17" t="s">
+        <v>86</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="D467" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E467" s="22" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F467" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G467" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H467" s="22" t="s">
         <v>15</v>
@@ -13903,25 +13902,25 @@
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B468" t="s">
-        <v>88</v>
+        <v>61</v>
+      </c>
+      <c r="B468" s="17" t="s">
+        <v>86</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="D468" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E468" s="22" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="F468" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G468" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H468" s="22" t="s">
         <v>15</v>
@@ -13929,79 +13928,79 @@
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B469" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C469" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D469" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E469" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F469" s="22" t="s">
+        <v>369</v>
+      </c>
+      <c r="G469" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="H469" s="22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A470" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B470" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C470" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D470" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E470" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F470" s="32" t="s">
+        <v>370</v>
+      </c>
+      <c r="G470" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="H470" s="32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A471" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B469" t="s">
+      <c r="B471" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="C469" s="4" t="s">
+      <c r="C471" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D469" s="20" t="s">
+      <c r="D471" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="E469" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F469" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G469" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H469" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A470" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B470" t="s">
-        <v>88</v>
-      </c>
-      <c r="C470" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D470" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E470" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F470" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G470" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H470" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A471" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B471" t="s">
-        <v>88</v>
-      </c>
-      <c r="C471" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D471" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E471" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F471" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G471" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H471" s="22" t="s">
+      <c r="E471" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="F471" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G471" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H471" s="29" t="s">
         <v>15</v>
       </c>
     </row>
@@ -14009,17 +14008,17 @@
       <c r="A472" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B472" t="s">
-        <v>89</v>
+      <c r="B472" s="17" t="s">
+        <v>88</v>
       </c>
       <c r="C472" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D472" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E472" s="22" t="s">
-        <v>15</v>
+        <v>343</v>
       </c>
       <c r="F472" s="22" t="s">
         <v>15</v>
@@ -14035,17 +14034,17 @@
       <c r="A473" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B473" t="s">
-        <v>89</v>
+      <c r="B473" s="17" t="s">
+        <v>88</v>
       </c>
       <c r="C473" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D473" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E473" s="22" t="s">
-        <v>15</v>
+        <v>329</v>
       </c>
       <c r="F473" s="22" t="s">
         <v>15</v>
@@ -14061,17 +14060,17 @@
       <c r="A474" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B474" t="s">
-        <v>89</v>
+      <c r="B474" s="17" t="s">
+        <v>88</v>
       </c>
       <c r="C474" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D474" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E474" s="22" t="s">
-        <v>15</v>
+        <v>259</v>
       </c>
       <c r="F474" s="22" t="s">
         <v>15</v>
@@ -14087,17 +14086,17 @@
       <c r="A475" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B475" t="s">
-        <v>89</v>
+      <c r="B475" s="17" t="s">
+        <v>88</v>
       </c>
       <c r="C475" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D475" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E475" s="22" t="s">
-        <v>15</v>
+        <v>249</v>
       </c>
       <c r="F475" s="22" t="s">
         <v>15</v>
@@ -14113,17 +14112,17 @@
       <c r="A476" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B476" t="s">
-        <v>89</v>
+      <c r="B476" s="17" t="s">
+        <v>88</v>
       </c>
       <c r="C476" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D476" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E476" s="22" t="s">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="F476" s="22" t="s">
         <v>15</v>
@@ -14139,17 +14138,17 @@
       <c r="A477" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B477" t="s">
-        <v>89</v>
+      <c r="B477" s="17" t="s">
+        <v>88</v>
       </c>
       <c r="C477" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D477" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E477" s="22" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="F477" s="22" t="s">
         <v>15</v>
@@ -14165,20 +14164,20 @@
       <c r="A478" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B478" t="s">
-        <v>89</v>
+      <c r="B478" s="17" t="s">
+        <v>88</v>
       </c>
       <c r="C478" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D478" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E478" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F478" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G478" s="22" t="s">
         <v>15</v>
@@ -14191,20 +14190,20 @@
       <c r="A479" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B479" t="s">
-        <v>89</v>
+      <c r="B479" s="17" t="s">
+        <v>88</v>
       </c>
       <c r="C479" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D479" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E479" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F479" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G479" s="22" t="s">
         <v>15</v>
@@ -14217,7 +14216,7 @@
       <c r="A480" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B480" t="s">
+      <c r="B480" s="17" t="s">
         <v>89</v>
       </c>
       <c r="C480" s="4" t="s">
@@ -14227,10 +14226,10 @@
         <v>25</v>
       </c>
       <c r="E480" s="22" t="s">
-        <v>15</v>
+        <v>329</v>
       </c>
       <c r="F480" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G480" s="22" t="s">
         <v>15</v>
@@ -14243,20 +14242,20 @@
       <c r="A481" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B481" t="s">
-        <v>90</v>
+      <c r="B481" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="C481" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D481" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E481" s="22" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F481" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G481" s="22" t="s">
         <v>15</v>
@@ -14269,20 +14268,20 @@
       <c r="A482" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B482" t="s">
-        <v>90</v>
+      <c r="B482" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="C482" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D482" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E482" s="22" t="s">
-        <v>15</v>
+        <v>249</v>
       </c>
       <c r="F482" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G482" s="22" t="s">
         <v>15</v>
@@ -14295,20 +14294,20 @@
       <c r="A483" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B483" t="s">
-        <v>90</v>
+      <c r="B483" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="C483" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D483" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E483" s="22" t="s">
-        <v>15</v>
+        <v>343</v>
       </c>
       <c r="F483" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G483" s="22" t="s">
         <v>15</v>
@@ -14321,20 +14320,20 @@
       <c r="A484" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B484" t="s">
-        <v>90</v>
+      <c r="B484" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="C484" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D484" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E484" s="22" t="s">
-        <v>15</v>
+        <v>259</v>
       </c>
       <c r="F484" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G484" s="22" t="s">
         <v>15</v>
@@ -14347,20 +14346,20 @@
       <c r="A485" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B485" t="s">
-        <v>90</v>
+      <c r="B485" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="C485" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D485" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E485" s="22" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="F485" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G485" s="22" t="s">
         <v>15</v>
@@ -14373,20 +14372,20 @@
       <c r="A486" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B486" t="s">
-        <v>90</v>
+      <c r="B486" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="C486" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D486" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E486" s="22" t="s">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="F486" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G486" s="22" t="s">
         <v>15</v>
@@ -14399,23 +14398,23 @@
       <c r="A487" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B487" t="s">
-        <v>90</v>
+      <c r="B487" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="C487" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D487" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E487" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F487" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G487" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H487" s="22" t="s">
         <v>15</v>
@@ -14425,23 +14424,23 @@
       <c r="A488" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B488" t="s">
-        <v>90</v>
+      <c r="B488" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="C488" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D488" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E488" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F488" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G488" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H488" s="22" t="s">
         <v>15</v>
@@ -14451,7 +14450,7 @@
       <c r="A489" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B489" t="s">
+      <c r="B489" s="17" t="s">
         <v>90</v>
       </c>
       <c r="C489" s="4" t="s">
@@ -14461,10 +14460,10 @@
         <v>28</v>
       </c>
       <c r="E489" s="22" t="s">
-        <v>15</v>
+        <v>249</v>
       </c>
       <c r="F489" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G489" s="22" t="s">
         <v>15</v>
@@ -14477,20 +14476,20 @@
       <c r="A490" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B490" t="s">
-        <v>91</v>
+      <c r="B490" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="C490" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D490" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E490" s="22" t="s">
-        <v>15</v>
+        <v>259</v>
       </c>
       <c r="F490" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G490" s="22" t="s">
         <v>15</v>
@@ -14503,20 +14502,20 @@
       <c r="A491" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B491" t="s">
-        <v>91</v>
+      <c r="B491" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="C491" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D491" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E491" s="22" t="s">
-        <v>15</v>
+        <v>343</v>
       </c>
       <c r="F491" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G491" s="22" t="s">
         <v>15</v>
@@ -14529,20 +14528,20 @@
       <c r="A492" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B492" t="s">
-        <v>91</v>
+      <c r="B492" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="C492" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D492" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E492" s="22" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="F492" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G492" s="22" t="s">
         <v>15</v>
@@ -14555,20 +14554,20 @@
       <c r="A493" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B493" t="s">
-        <v>91</v>
+      <c r="B493" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="C493" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D493" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E493" s="22" t="s">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="F493" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G493" s="22" t="s">
         <v>15</v>
@@ -14581,20 +14580,20 @@
       <c r="A494" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B494" t="s">
-        <v>91</v>
+      <c r="B494" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="C494" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D494" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E494" s="22" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F494" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G494" s="22" t="s">
         <v>15</v>
@@ -14607,20 +14606,20 @@
       <c r="A495" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B495" t="s">
-        <v>91</v>
+      <c r="B495" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="C495" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D495" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E495" s="22" t="s">
-        <v>15</v>
+        <v>329</v>
       </c>
       <c r="F495" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G495" s="22" t="s">
         <v>15</v>
@@ -14633,23 +14632,23 @@
       <c r="A496" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B496" t="s">
-        <v>91</v>
+      <c r="B496" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="C496" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D496" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E496" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F496" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G496" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H496" s="22" t="s">
         <v>15</v>
@@ -14659,23 +14658,23 @@
       <c r="A497" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B497" t="s">
-        <v>92</v>
+      <c r="B497" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="C497" s="4" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D497" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E497" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F497" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G497" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H497" s="22" t="s">
         <v>15</v>
@@ -14685,23 +14684,23 @@
       <c r="A498" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B498" t="s">
-        <v>92</v>
+      <c r="B498" s="17" t="s">
+        <v>91</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D498" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E498" s="22" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F498" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G498" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H498" s="22" t="s">
         <v>15</v>
@@ -14711,23 +14710,23 @@
       <c r="A499" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B499" t="s">
-        <v>92</v>
+      <c r="B499" s="17" t="s">
+        <v>91</v>
       </c>
       <c r="C499" s="4" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D499" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E499" s="22" t="s">
-        <v>15</v>
+        <v>343</v>
       </c>
       <c r="F499" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G499" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H499" s="22" t="s">
         <v>15</v>
@@ -14737,23 +14736,23 @@
       <c r="A500" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B500" t="s">
-        <v>92</v>
+      <c r="B500" s="17" t="s">
+        <v>91</v>
       </c>
       <c r="C500" s="4" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D500" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E500" s="22" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="F500" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G500" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H500" s="22" t="s">
         <v>15</v>
@@ -14763,23 +14762,23 @@
       <c r="A501" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B501" t="s">
-        <v>92</v>
+      <c r="B501" s="17" t="s">
+        <v>91</v>
       </c>
       <c r="C501" s="4" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D501" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E501" s="22" t="s">
-        <v>15</v>
+        <v>329</v>
       </c>
       <c r="F501" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G501" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H501" s="22" t="s">
         <v>15</v>
@@ -14789,23 +14788,23 @@
       <c r="A502" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B502" t="s">
-        <v>92</v>
+      <c r="B502" s="17" t="s">
+        <v>91</v>
       </c>
       <c r="C502" s="4" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D502" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E502" s="22" t="s">
-        <v>15</v>
+        <v>259</v>
       </c>
       <c r="F502" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G502" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H502" s="22" t="s">
         <v>15</v>
@@ -14815,23 +14814,23 @@
       <c r="A503" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B503" t="s">
-        <v>92</v>
+      <c r="B503" s="17" t="s">
+        <v>91</v>
       </c>
       <c r="C503" s="4" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D503" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E503" s="22" t="s">
-        <v>15</v>
+        <v>249</v>
       </c>
       <c r="F503" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G503" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H503" s="22" t="s">
         <v>15</v>
@@ -14841,23 +14840,23 @@
       <c r="A504" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B504" t="s">
-        <v>92</v>
+      <c r="B504" s="17" t="s">
+        <v>91</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D504" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E504" s="22" t="s">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="F504" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G504" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H504" s="22" t="s">
         <v>15</v>
@@ -14867,77 +14866,77 @@
       <c r="A505" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B505" t="s">
+      <c r="B505" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C505" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D505" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E505" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F505" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="G505" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H505" s="22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A506" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B506" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C506" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D506" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E506" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F506" s="32" t="s">
+        <v>372</v>
+      </c>
+      <c r="G506" s="32" t="s">
+        <v>368</v>
+      </c>
+      <c r="H506" s="32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A507" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B507" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C505" s="4" t="s">
+      <c r="C507" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D505" s="20" t="s">
+      <c r="D507" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="E505" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F505" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G505" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H505" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A506" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B506" t="s">
-        <v>93</v>
-      </c>
-      <c r="C506" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D506" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E506" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F506" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G506" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H506" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A507" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B507" t="s">
-        <v>93</v>
-      </c>
-      <c r="C507" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D507" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E507" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F507" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G507" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H507" s="22" t="s">
+      <c r="E507" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F507" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G507" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H507" s="29" t="s">
         <v>15</v>
       </c>
     </row>
@@ -14945,17 +14944,17 @@
       <c r="A508" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B508" t="s">
-        <v>93</v>
+      <c r="B508" s="17" t="s">
+        <v>92</v>
       </c>
       <c r="C508" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D508" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E508" s="22" t="s">
-        <v>15</v>
+        <v>259</v>
       </c>
       <c r="F508" s="22" t="s">
         <v>15</v>
@@ -14971,17 +14970,17 @@
       <c r="A509" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B509" t="s">
-        <v>93</v>
+      <c r="B509" s="17" t="s">
+        <v>92</v>
       </c>
       <c r="C509" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D509" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E509" s="22" t="s">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="F509" s="22" t="s">
         <v>15</v>
@@ -14997,17 +14996,17 @@
       <c r="A510" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B510" t="s">
-        <v>93</v>
+      <c r="B510" s="17" t="s">
+        <v>92</v>
       </c>
       <c r="C510" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D510" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E510" s="22" t="s">
-        <v>15</v>
+        <v>329</v>
       </c>
       <c r="F510" s="22" t="s">
         <v>15</v>
@@ -15023,17 +15022,17 @@
       <c r="A511" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B511" t="s">
-        <v>93</v>
+      <c r="B511" s="17" t="s">
+        <v>92</v>
       </c>
       <c r="C511" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D511" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E511" s="22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F511" s="22" t="s">
         <v>15</v>
@@ -15049,17 +15048,17 @@
       <c r="A512" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B512" t="s">
-        <v>93</v>
+      <c r="B512" s="17" t="s">
+        <v>92</v>
       </c>
       <c r="C512" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D512" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E512" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F512" s="22" t="s">
         <v>15</v>
@@ -15075,17 +15074,17 @@
       <c r="A513" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B513" t="s">
-        <v>93</v>
+      <c r="B513" s="17" t="s">
+        <v>92</v>
       </c>
       <c r="C513" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D513" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E513" s="22" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="F513" s="22" t="s">
         <v>15</v>
@@ -15101,20 +15100,20 @@
       <c r="A514" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B514" t="s">
-        <v>93</v>
+      <c r="B514" s="17" t="s">
+        <v>92</v>
       </c>
       <c r="C514" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D514" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E514" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F514" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G514" s="22" t="s">
         <v>15</v>
@@ -15127,20 +15126,20 @@
       <c r="A515" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B515" t="s">
-        <v>94</v>
+      <c r="B515" s="17" t="s">
+        <v>92</v>
       </c>
       <c r="C515" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D515" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E515" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F515" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G515" s="22" t="s">
         <v>15</v>
@@ -15153,20 +15152,20 @@
       <c r="A516" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B516" t="s">
-        <v>94</v>
+      <c r="B516" s="17" t="s">
+        <v>93</v>
       </c>
       <c r="C516" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D516" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E516" s="22" t="s">
-        <v>15</v>
+        <v>329</v>
       </c>
       <c r="F516" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G516" s="22" t="s">
         <v>15</v>
@@ -15179,20 +15178,20 @@
       <c r="A517" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B517" t="s">
-        <v>94</v>
+      <c r="B517" s="17" t="s">
+        <v>93</v>
       </c>
       <c r="C517" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D517" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E517" s="22" t="s">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="F517" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G517" s="22" t="s">
         <v>15</v>
@@ -15205,20 +15204,20 @@
       <c r="A518" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B518" t="s">
-        <v>94</v>
+      <c r="B518" s="17" t="s">
+        <v>93</v>
       </c>
       <c r="C518" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D518" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E518" s="22" t="s">
-        <v>15</v>
+        <v>259</v>
       </c>
       <c r="F518" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G518" s="22" t="s">
         <v>15</v>
@@ -15231,20 +15230,20 @@
       <c r="A519" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B519" t="s">
-        <v>94</v>
+      <c r="B519" s="17" t="s">
+        <v>93</v>
       </c>
       <c r="C519" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D519" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E519" s="22" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="F519" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G519" s="22" t="s">
         <v>15</v>
@@ -15257,20 +15256,20 @@
       <c r="A520" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B520" t="s">
-        <v>94</v>
+      <c r="B520" s="17" t="s">
+        <v>93</v>
       </c>
       <c r="C520" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D520" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E520" s="22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F520" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G520" s="22" t="s">
         <v>15</v>
@@ -15283,20 +15282,20 @@
       <c r="A521" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B521" t="s">
-        <v>94</v>
+      <c r="B521" s="17" t="s">
+        <v>93</v>
       </c>
       <c r="C521" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D521" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E521" s="22" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F521" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G521" s="22" t="s">
         <v>15</v>
@@ -15309,20 +15308,20 @@
       <c r="A522" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B522" t="s">
-        <v>94</v>
+      <c r="B522" s="17" t="s">
+        <v>93</v>
       </c>
       <c r="C522" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D522" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E522" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F522" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G522" s="22" t="s">
         <v>15</v>
@@ -15335,23 +15334,23 @@
       <c r="A523" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B523" t="s">
-        <v>94</v>
+      <c r="B523" s="17" t="s">
+        <v>93</v>
       </c>
       <c r="C523" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D523" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E523" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F523" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G523" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H523" s="22" t="s">
         <v>15</v>
@@ -15361,23 +15360,23 @@
       <c r="A524" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B524" t="s">
-        <v>95</v>
+      <c r="B524" s="17" t="s">
+        <v>93</v>
       </c>
       <c r="C524" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D524" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E524" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F524" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G524" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H524" s="22" t="s">
         <v>15</v>
@@ -15387,20 +15386,20 @@
       <c r="A525" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B525" t="s">
-        <v>95</v>
+      <c r="B525" s="17" t="s">
+        <v>94</v>
       </c>
       <c r="C525" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D525" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E525" s="22" t="s">
-        <v>15</v>
+        <v>329</v>
       </c>
       <c r="F525" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G525" s="22" t="s">
         <v>15</v>
@@ -15413,20 +15412,20 @@
       <c r="A526" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B526" t="s">
-        <v>95</v>
+      <c r="B526" s="17" t="s">
+        <v>94</v>
       </c>
       <c r="C526" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D526" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E526" s="22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F526" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G526" s="22" t="s">
         <v>15</v>
@@ -15439,20 +15438,20 @@
       <c r="A527" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B527" t="s">
-        <v>95</v>
+      <c r="B527" s="17" t="s">
+        <v>94</v>
       </c>
       <c r="C527" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D527" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E527" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F527" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G527" s="22" t="s">
         <v>15</v>
@@ -15465,20 +15464,20 @@
       <c r="A528" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B528" t="s">
-        <v>95</v>
+      <c r="B528" s="17" t="s">
+        <v>94</v>
       </c>
       <c r="C528" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D528" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E528" s="22" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="F528" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G528" s="22" t="s">
         <v>15</v>
@@ -15491,20 +15490,20 @@
       <c r="A529" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B529" t="s">
-        <v>95</v>
+      <c r="B529" s="17" t="s">
+        <v>94</v>
       </c>
       <c r="C529" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D529" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E529" s="22" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F529" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G529" s="22" t="s">
         <v>15</v>
@@ -15517,20 +15516,20 @@
       <c r="A530" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B530" t="s">
-        <v>95</v>
+      <c r="B530" s="17" t="s">
+        <v>94</v>
       </c>
       <c r="C530" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D530" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E530" s="22" t="s">
-        <v>15</v>
+        <v>259</v>
       </c>
       <c r="F530" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G530" s="22" t="s">
         <v>15</v>
@@ -15543,20 +15542,20 @@
       <c r="A531" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B531" t="s">
-        <v>96</v>
+      <c r="B531" s="17" t="s">
+        <v>94</v>
       </c>
       <c r="C531" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D531" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E531" s="22" t="s">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="F531" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G531" s="22" t="s">
         <v>15</v>
@@ -15569,23 +15568,23 @@
       <c r="A532" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B532" t="s">
-        <v>96</v>
+      <c r="B532" s="17" t="s">
+        <v>94</v>
       </c>
       <c r="C532" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D532" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E532" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F532" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G532" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H532" s="22" t="s">
         <v>15</v>
@@ -15595,23 +15594,23 @@
       <c r="A533" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B533" t="s">
-        <v>96</v>
+      <c r="B533" s="17" t="s">
+        <v>94</v>
       </c>
       <c r="C533" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D533" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E533" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F533" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G533" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H533" s="22" t="s">
         <v>15</v>
@@ -15621,23 +15620,23 @@
       <c r="A534" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B534" t="s">
-        <v>96</v>
+      <c r="B534" s="17" t="s">
+        <v>95</v>
       </c>
       <c r="C534" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D534" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E534" s="22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F534" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G534" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H534" s="22" t="s">
         <v>15</v>
@@ -15647,23 +15646,23 @@
       <c r="A535" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B535" t="s">
-        <v>96</v>
+      <c r="B535" s="17" t="s">
+        <v>95</v>
       </c>
       <c r="C535" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D535" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E535" s="22" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F535" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G535" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H535" s="22" t="s">
         <v>15</v>
@@ -15673,23 +15672,23 @@
       <c r="A536" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B536" t="s">
-        <v>96</v>
+      <c r="B536" s="17" t="s">
+        <v>95</v>
       </c>
       <c r="C536" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D536" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E536" s="22" t="s">
-        <v>15</v>
+        <v>329</v>
       </c>
       <c r="F536" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G536" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H536" s="22" t="s">
         <v>15</v>
@@ -15699,23 +15698,23 @@
       <c r="A537" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B537" t="s">
-        <v>96</v>
+      <c r="B537" s="17" t="s">
+        <v>95</v>
       </c>
       <c r="C537" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D537" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E537" s="22" t="s">
-        <v>15</v>
+        <v>259</v>
       </c>
       <c r="F537" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G537" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H537" s="22" t="s">
         <v>15</v>
@@ -15725,23 +15724,23 @@
       <c r="A538" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B538" t="s">
-        <v>96</v>
+      <c r="B538" s="17" t="s">
+        <v>95</v>
       </c>
       <c r="C538" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D538" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E538" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F538" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G538" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H538" s="22" t="s">
         <v>15</v>
@@ -15751,23 +15750,23 @@
       <c r="A539" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B539" t="s">
-        <v>96</v>
+      <c r="B539" s="17" t="s">
+        <v>95</v>
       </c>
       <c r="C539" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D539" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E539" s="22" t="s">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="F539" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G539" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H539" s="22" t="s">
         <v>15</v>
@@ -15777,23 +15776,23 @@
       <c r="A540" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B540" t="s">
-        <v>97</v>
+      <c r="B540" s="17" t="s">
+        <v>95</v>
       </c>
       <c r="C540" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D540" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E540" s="22" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F540" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G540" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H540" s="22" t="s">
         <v>15</v>
@@ -15803,69 +15802,69 @@
       <c r="A541" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B541" t="s">
-        <v>97</v>
+      <c r="B541" s="17" t="s">
+        <v>95</v>
       </c>
       <c r="C541" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D541" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E541" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F541" s="22" t="s">
+        <v>369</v>
+      </c>
+      <c r="G541" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="H541" s="22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A542" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B542" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C542" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D542" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E542" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F542" s="32" t="s">
+        <v>370</v>
+      </c>
+      <c r="G542" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="H542" s="32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="543" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A543" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B543" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C543" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D541" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E541" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F541" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G541" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H541" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A542" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B542" t="s">
-        <v>97</v>
-      </c>
-      <c r="C542" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D542" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E542" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F542" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G542" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H542" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="543" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A543" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B543" t="s">
-        <v>97</v>
-      </c>
-      <c r="C543" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D543" s="20" t="s">
-        <v>25</v>
+      <c r="D543" s="19" t="s">
+        <v>13</v>
       </c>
       <c r="E543" s="22" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="F543" s="22" t="s">
         <v>15</v>
@@ -15881,17 +15880,17 @@
       <c r="A544" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B544" t="s">
-        <v>97</v>
+      <c r="B544" s="17" t="s">
+        <v>96</v>
       </c>
       <c r="C544" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D544" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E544" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F544" s="22" t="s">
         <v>15</v>
@@ -15907,17 +15906,17 @@
       <c r="A545" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B545" t="s">
-        <v>97</v>
+      <c r="B545" s="17" t="s">
+        <v>96</v>
       </c>
       <c r="C545" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D545" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E545" s="22" t="s">
-        <v>15</v>
+        <v>286</v>
       </c>
       <c r="F545" s="22" t="s">
         <v>15</v>
@@ -15933,17 +15932,17 @@
       <c r="A546" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B546" t="s">
-        <v>97</v>
+      <c r="B546" s="17" t="s">
+        <v>96</v>
       </c>
       <c r="C546" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D546" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E546" s="22" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="F546" s="22" t="s">
         <v>15</v>
@@ -15959,17 +15958,17 @@
       <c r="A547" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B547" t="s">
-        <v>97</v>
+      <c r="B547" s="17" t="s">
+        <v>96</v>
       </c>
       <c r="C547" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D547" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E547" s="22" t="s">
-        <v>15</v>
+        <v>248</v>
       </c>
       <c r="F547" s="22" t="s">
         <v>15</v>
@@ -15985,17 +15984,17 @@
       <c r="A548" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B548" t="s">
-        <v>97</v>
+      <c r="B548" s="17" t="s">
+        <v>96</v>
       </c>
       <c r="C548" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D548" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E548" s="22" t="s">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="F548" s="22" t="s">
         <v>15</v>
@@ -16011,17 +16010,17 @@
       <c r="A549" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B549" t="s">
-        <v>98</v>
+      <c r="B549" s="17" t="s">
+        <v>96</v>
       </c>
       <c r="C549" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D549" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E549" s="22" t="s">
-        <v>15</v>
+        <v>329</v>
       </c>
       <c r="F549" s="22" t="s">
         <v>15</v>
@@ -16037,20 +16036,20 @@
       <c r="A550" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B550" t="s">
-        <v>98</v>
+      <c r="B550" s="17" t="s">
+        <v>96</v>
       </c>
       <c r="C550" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D550" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E550" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F550" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G550" s="22" t="s">
         <v>15</v>
@@ -16063,20 +16062,20 @@
       <c r="A551" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B551" t="s">
-        <v>98</v>
+      <c r="B551" s="17" t="s">
+        <v>96</v>
       </c>
       <c r="C551" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D551" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E551" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F551" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G551" s="22" t="s">
         <v>15</v>
@@ -16089,20 +16088,20 @@
       <c r="A552" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B552" t="s">
-        <v>98</v>
+      <c r="B552" s="17" t="s">
+        <v>97</v>
       </c>
       <c r="C552" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D552" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E552" s="22" t="s">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="F552" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G552" s="22" t="s">
         <v>15</v>
@@ -16115,20 +16114,20 @@
       <c r="A553" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B553" t="s">
-        <v>98</v>
+      <c r="B553" s="17" t="s">
+        <v>97</v>
       </c>
       <c r="C553" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D553" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E553" s="22" t="s">
-        <v>15</v>
+        <v>286</v>
       </c>
       <c r="F553" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G553" s="22" t="s">
         <v>15</v>
@@ -16141,20 +16140,20 @@
       <c r="A554" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B554" t="s">
-        <v>98</v>
+      <c r="B554" s="17" t="s">
+        <v>97</v>
       </c>
       <c r="C554" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D554" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E554" s="22" t="s">
-        <v>15</v>
+        <v>248</v>
       </c>
       <c r="F554" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G554" s="22" t="s">
         <v>15</v>
@@ -16167,20 +16166,20 @@
       <c r="A555" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B555" t="s">
-        <v>98</v>
+      <c r="B555" s="17" t="s">
+        <v>97</v>
       </c>
       <c r="C555" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D555" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E555" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F555" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G555" s="22" t="s">
         <v>15</v>
@@ -16193,20 +16192,20 @@
       <c r="A556" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B556" t="s">
-        <v>98</v>
+      <c r="B556" s="17" t="s">
+        <v>97</v>
       </c>
       <c r="C556" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D556" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E556" s="22" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="F556" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G556" s="22" t="s">
         <v>15</v>
@@ -16219,20 +16218,20 @@
       <c r="A557" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B557" t="s">
-        <v>98</v>
+      <c r="B557" s="17" t="s">
+        <v>97</v>
       </c>
       <c r="C557" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D557" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E557" s="22" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="F557" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G557" s="22" t="s">
         <v>15</v>
@@ -16245,20 +16244,20 @@
       <c r="A558" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B558" t="s">
-        <v>99</v>
+      <c r="B558" s="17" t="s">
+        <v>97</v>
       </c>
       <c r="C558" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D558" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E558" s="22" t="s">
-        <v>15</v>
+        <v>329</v>
       </c>
       <c r="F558" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G558" s="22" t="s">
         <v>15</v>
@@ -16271,23 +16270,23 @@
       <c r="A559" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B559" t="s">
-        <v>99</v>
+      <c r="B559" s="17" t="s">
+        <v>97</v>
       </c>
       <c r="C559" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D559" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E559" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F559" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="G559" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H559" s="22" t="s">
         <v>15</v>
@@ -16297,23 +16296,23 @@
       <c r="A560" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B560" t="s">
-        <v>99</v>
+      <c r="B560" s="17" t="s">
+        <v>97</v>
       </c>
       <c r="C560" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D560" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E560" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F560" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G560" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H560" s="22" t="s">
         <v>15</v>
@@ -16323,20 +16322,20 @@
       <c r="A561" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B561" t="s">
-        <v>99</v>
+      <c r="B561" s="17" t="s">
+        <v>98</v>
       </c>
       <c r="C561" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D561" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E561" s="22" t="s">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="F561" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G561" s="22" t="s">
         <v>15</v>
@@ -16349,20 +16348,20 @@
       <c r="A562" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B562" t="s">
-        <v>99</v>
+      <c r="B562" s="17" t="s">
+        <v>98</v>
       </c>
       <c r="C562" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D562" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E562" s="22" t="s">
-        <v>15</v>
+        <v>286</v>
       </c>
       <c r="F562" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G562" s="22" t="s">
         <v>15</v>
@@ -16375,20 +16374,20 @@
       <c r="A563" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B563" t="s">
-        <v>99</v>
+      <c r="B563" s="17" t="s">
+        <v>98</v>
       </c>
       <c r="C563" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D563" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E563" s="22" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="F563" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G563" s="22" t="s">
         <v>15</v>
@@ -16401,20 +16400,20 @@
       <c r="A564" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B564" t="s">
-        <v>100</v>
+      <c r="B564" s="17" t="s">
+        <v>98</v>
       </c>
       <c r="C564" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D564" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E564" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F564" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G564" s="22" t="s">
         <v>15</v>
@@ -16427,20 +16426,20 @@
       <c r="A565" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B565" t="s">
-        <v>100</v>
+      <c r="B565" s="17" t="s">
+        <v>98</v>
       </c>
       <c r="C565" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D565" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E565" s="22" t="s">
-        <v>15</v>
+        <v>329</v>
       </c>
       <c r="F565" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G565" s="22" t="s">
         <v>15</v>
@@ -16453,20 +16452,20 @@
       <c r="A566" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B566" t="s">
-        <v>100</v>
+      <c r="B566" s="17" t="s">
+        <v>98</v>
       </c>
       <c r="C566" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D566" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E566" s="22" t="s">
-        <v>15</v>
+        <v>248</v>
       </c>
       <c r="F566" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G566" s="22" t="s">
         <v>15</v>
@@ -16479,20 +16478,20 @@
       <c r="A567" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B567" t="s">
-        <v>100</v>
+      <c r="B567" s="17" t="s">
+        <v>98</v>
       </c>
       <c r="C567" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D567" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E567" s="22" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="F567" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G567" s="22" t="s">
         <v>15</v>
@@ -16505,23 +16504,23 @@
       <c r="A568" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B568" t="s">
-        <v>100</v>
+      <c r="B568" s="17" t="s">
+        <v>98</v>
       </c>
       <c r="C568" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D568" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E568" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F568" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G568" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H568" s="22" t="s">
         <v>15</v>
@@ -16531,23 +16530,23 @@
       <c r="A569" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B569" t="s">
-        <v>100</v>
+      <c r="B569" s="17" t="s">
+        <v>98</v>
       </c>
       <c r="C569" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D569" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E569" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F569" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G569" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H569" s="22" t="s">
         <v>15</v>
@@ -16557,23 +16556,23 @@
       <c r="A570" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B570" t="s">
-        <v>100</v>
+      <c r="B570" s="17" t="s">
+        <v>99</v>
       </c>
       <c r="C570" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D570" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E570" s="22" t="s">
-        <v>15</v>
+        <v>248</v>
       </c>
       <c r="F570" s="22" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="G570" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H570" s="22" t="s">
         <v>15</v>
@@ -16583,23 +16582,23 @@
       <c r="A571" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B571" t="s">
-        <v>100</v>
+      <c r="B571" s="17" t="s">
+        <v>99</v>
       </c>
       <c r="C571" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D571" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E571" s="22" t="s">
-        <v>15</v>
+        <v>357</v>
       </c>
       <c r="F571" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G571" s="22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H571" s="22" t="s">
         <v>15</v>
@@ -16609,23 +16608,23 @@
       <c r="A572" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B572" t="s">
-        <v>100</v>
+      <c r="B572" s="17" t="s">
+        <v>99</v>
       </c>
       <c r="C572" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D572" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E572" s="22" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="F572" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G572" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H572" s="22" t="s">
         <v>15</v>
@@ -16635,23 +16634,23 @@
       <c r="A573" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B573" t="s">
-        <v>101</v>
+      <c r="B573" s="17" t="s">
+        <v>99</v>
       </c>
       <c r="C573" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D573" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E573" s="22" t="s">
-        <v>15</v>
+        <v>329</v>
       </c>
       <c r="F573" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G573" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H573" s="22" t="s">
         <v>15</v>
@@ -16661,23 +16660,23 @@
       <c r="A574" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B574" t="s">
-        <v>101</v>
+      <c r="B574" s="17" t="s">
+        <v>99</v>
       </c>
       <c r="C574" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D574" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E574" s="22" t="s">
-        <v>15</v>
+        <v>286</v>
       </c>
       <c r="F574" s="22" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
       <c r="G574" s="22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H574" s="22" t="s">
         <v>15</v>
@@ -16687,23 +16686,23 @@
       <c r="A575" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B575" t="s">
-        <v>101</v>
+      <c r="B575" s="17" t="s">
+        <v>99</v>
       </c>
       <c r="C575" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D575" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E575" s="22" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F575" s="22" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G575" s="22" t="s">
-        <v>15</v>
+        <v>368</v>
       </c>
       <c r="H575" s="22" t="s">
         <v>15</v>
@@ -16713,23 +16712,23 @@
       <c r="A576" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B576" t="s">
-        <v>101</v>
+      <c r="B576" s="17" t="s">
+        <v>99</v>
       </c>
       <c r="C576" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D576" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E576" s="22" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="F576" s="22" t="s">
-        <v>15</v>
+        <v>369</v>
       </c>
       <c r="G576" s="22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H576" s="22" t="s">
         <v>15</v>
@@ -16739,77 +16738,77 @@
       <c r="A577" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B577" t="s">
-        <v>101</v>
+      <c r="B577" s="17" t="s">
+        <v>99</v>
       </c>
       <c r="C577" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D577" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E577" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F577" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="G577" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="H577" s="22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="578" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A578" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B578" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C578" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D578" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E578" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F578" s="22" t="s">
+        <v>372</v>
+      </c>
+      <c r="G578" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="H578" s="22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="579" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A579" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B579" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C579" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D577" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E577" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F577" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G577" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H577" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="578" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A578" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B578" t="s">
-        <v>101</v>
-      </c>
-      <c r="C578" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D578" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E578" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F578" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G578" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H578" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="579" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A579" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B579" t="s">
-        <v>101</v>
-      </c>
-      <c r="C579" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D579" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E579" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F579" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G579" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H579" s="22" t="s">
+      <c r="D579" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E579" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="F579" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G579" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H579" s="29" t="s">
         <v>15</v>
       </c>
     </row>
@@ -16817,14 +16816,14 @@
       <c r="A580" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B580" t="s">
-        <v>101</v>
+      <c r="B580" s="17" t="s">
+        <v>100</v>
       </c>
       <c r="C580" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D580" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E580" s="22" t="s">
         <v>15</v>
@@ -16843,14 +16842,14 @@
       <c r="A581" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B581" t="s">
-        <v>101</v>
+      <c r="B581" s="17" t="s">
+        <v>100</v>
       </c>
       <c r="C581" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D581" s="20" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E581" s="22" t="s">
         <v>15</v>
@@ -16869,14 +16868,14 @@
       <c r="A582" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B582" t="s">
-        <v>102</v>
+      <c r="B582" s="17" t="s">
+        <v>100</v>
       </c>
       <c r="C582" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D582" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E582" s="22" t="s">
         <v>15</v>
@@ -16895,14 +16894,14 @@
       <c r="A583" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B583" t="s">
-        <v>102</v>
+      <c r="B583" s="17" t="s">
+        <v>100</v>
       </c>
       <c r="C583" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D583" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E583" s="22" t="s">
         <v>15</v>
@@ -16921,14 +16920,14 @@
       <c r="A584" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B584" t="s">
-        <v>102</v>
+      <c r="B584" s="17" t="s">
+        <v>100</v>
       </c>
       <c r="C584" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D584" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E584" s="22" t="s">
         <v>15</v>
@@ -16947,14 +16946,14 @@
       <c r="A585" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B585" t="s">
-        <v>102</v>
+      <c r="B585" s="17" t="s">
+        <v>100</v>
       </c>
       <c r="C585" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D585" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E585" s="22" t="s">
         <v>15</v>
@@ -16973,14 +16972,14 @@
       <c r="A586" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B586" t="s">
-        <v>102</v>
+      <c r="B586" s="17" t="s">
+        <v>100</v>
       </c>
       <c r="C586" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D586" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E586" s="22" t="s">
         <v>15</v>
@@ -16999,14 +16998,14 @@
       <c r="A587" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B587" t="s">
-        <v>102</v>
+      <c r="B587" s="17" t="s">
+        <v>100</v>
       </c>
       <c r="C587" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D587" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E587" s="22" t="s">
         <v>15</v>
@@ -17025,14 +17024,14 @@
       <c r="A588" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B588" t="s">
-        <v>102</v>
+      <c r="B588" s="17" t="s">
+        <v>101</v>
       </c>
       <c r="C588" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D588" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E588" s="22" t="s">
         <v>15</v>
@@ -17051,14 +17050,14 @@
       <c r="A589" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B589" t="s">
-        <v>102</v>
+      <c r="B589" s="17" t="s">
+        <v>101</v>
       </c>
       <c r="C589" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D589" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E589" s="22" t="s">
         <v>15</v>
@@ -17077,14 +17076,14 @@
       <c r="A590" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B590" t="s">
-        <v>102</v>
+      <c r="B590" s="17" t="s">
+        <v>101</v>
       </c>
       <c r="C590" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D590" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E590" s="22" t="s">
         <v>15</v>
@@ -17103,14 +17102,14 @@
       <c r="A591" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B591" t="s">
-        <v>103</v>
+      <c r="B591" s="17" t="s">
+        <v>101</v>
       </c>
       <c r="C591" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D591" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E591" s="22" t="s">
         <v>15</v>
@@ -17129,14 +17128,14 @@
       <c r="A592" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B592" t="s">
-        <v>103</v>
+      <c r="B592" s="17" t="s">
+        <v>101</v>
       </c>
       <c r="C592" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D592" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E592" s="22" t="s">
         <v>15</v>
@@ -17155,14 +17154,14 @@
       <c r="A593" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B593" t="s">
-        <v>103</v>
+      <c r="B593" s="17" t="s">
+        <v>101</v>
       </c>
       <c r="C593" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D593" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E593" s="22" t="s">
         <v>15</v>
@@ -17181,14 +17180,14 @@
       <c r="A594" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B594" t="s">
-        <v>103</v>
+      <c r="B594" s="17" t="s">
+        <v>101</v>
       </c>
       <c r="C594" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D594" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E594" s="22" t="s">
         <v>15</v>
@@ -17207,14 +17206,14 @@
       <c r="A595" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B595" t="s">
-        <v>103</v>
+      <c r="B595" s="17" t="s">
+        <v>101</v>
       </c>
       <c r="C595" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D595" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E595" s="22" t="s">
         <v>15</v>
@@ -17233,14 +17232,14 @@
       <c r="A596" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B596" t="s">
-        <v>103</v>
+      <c r="B596" s="17" t="s">
+        <v>101</v>
       </c>
       <c r="C596" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D596" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E596" s="22" t="s">
         <v>15</v>
@@ -17259,14 +17258,14 @@
       <c r="A597" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B597" t="s">
-        <v>103</v>
+      <c r="B597" s="17" t="s">
+        <v>102</v>
       </c>
       <c r="C597" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D597" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E597" s="22" t="s">
         <v>15</v>
@@ -17285,14 +17284,14 @@
       <c r="A598" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B598" t="s">
-        <v>104</v>
+      <c r="B598" s="17" t="s">
+        <v>102</v>
       </c>
       <c r="C598" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D598" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E598" s="22" t="s">
         <v>15</v>
@@ -17311,14 +17310,14 @@
       <c r="A599" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B599" t="s">
-        <v>104</v>
+      <c r="B599" s="17" t="s">
+        <v>102</v>
       </c>
       <c r="C599" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D599" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E599" s="22" t="s">
         <v>15</v>
@@ -17337,14 +17336,14 @@
       <c r="A600" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B600" t="s">
-        <v>104</v>
+      <c r="B600" s="17" t="s">
+        <v>102</v>
       </c>
       <c r="C600" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D600" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E600" s="22" t="s">
         <v>15</v>
@@ -17363,14 +17362,14 @@
       <c r="A601" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B601" t="s">
-        <v>104</v>
+      <c r="B601" s="17" t="s">
+        <v>102</v>
       </c>
       <c r="C601" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D601" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E601" s="22" t="s">
         <v>15</v>
@@ -17389,14 +17388,14 @@
       <c r="A602" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B602" t="s">
-        <v>104</v>
+      <c r="B602" s="17" t="s">
+        <v>102</v>
       </c>
       <c r="C602" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D602" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E602" s="22" t="s">
         <v>15</v>
@@ -17415,14 +17414,14 @@
       <c r="A603" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B603" t="s">
-        <v>104</v>
+      <c r="B603" s="17" t="s">
+        <v>102</v>
       </c>
       <c r="C603" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D603" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E603" s="22" t="s">
         <v>15</v>
@@ -17441,14 +17440,14 @@
       <c r="A604" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B604" t="s">
-        <v>104</v>
+      <c r="B604" s="17" t="s">
+        <v>102</v>
       </c>
       <c r="C604" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D604" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E604" s="22" t="s">
         <v>15</v>
@@ -17467,14 +17466,14 @@
       <c r="A605" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B605" t="s">
-        <v>104</v>
+      <c r="B605" s="17" t="s">
+        <v>102</v>
       </c>
       <c r="C605" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D605" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E605" s="22" t="s">
         <v>15</v>
@@ -17493,14 +17492,14 @@
       <c r="A606" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B606" t="s">
-        <v>104</v>
+      <c r="B606" s="17" t="s">
+        <v>103</v>
       </c>
       <c r="C606" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D606" s="20" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E606" s="22" t="s">
         <v>15</v>
@@ -17519,14 +17518,14 @@
       <c r="A607" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B607" t="s">
-        <v>105</v>
+      <c r="B607" s="17" t="s">
+        <v>103</v>
       </c>
       <c r="C607" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D607" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E607" s="22" t="s">
         <v>15</v>
@@ -17545,14 +17544,14 @@
       <c r="A608" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B608" t="s">
-        <v>105</v>
+      <c r="B608" s="17" t="s">
+        <v>103</v>
       </c>
       <c r="C608" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D608" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E608" s="22" t="s">
         <v>15</v>
@@ -17571,14 +17570,14 @@
       <c r="A609" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B609" t="s">
-        <v>105</v>
+      <c r="B609" s="17" t="s">
+        <v>103</v>
       </c>
       <c r="C609" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D609" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E609" s="22" t="s">
         <v>15</v>
@@ -17597,14 +17596,14 @@
       <c r="A610" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B610" t="s">
-        <v>105</v>
+      <c r="B610" s="17" t="s">
+        <v>103</v>
       </c>
       <c r="C610" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D610" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E610" s="22" t="s">
         <v>15</v>
@@ -17623,14 +17622,14 @@
       <c r="A611" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B611" t="s">
-        <v>105</v>
+      <c r="B611" s="17" t="s">
+        <v>103</v>
       </c>
       <c r="C611" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D611" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E611" s="22" t="s">
         <v>15</v>
@@ -17649,14 +17648,14 @@
       <c r="A612" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B612" t="s">
-        <v>105</v>
+      <c r="B612" s="17" t="s">
+        <v>103</v>
       </c>
       <c r="C612" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D612" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E612" s="22" t="s">
         <v>15</v>
@@ -17675,77 +17674,77 @@
       <c r="A613" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B613" t="s">
-        <v>105</v>
+      <c r="B613" s="17" t="s">
+        <v>103</v>
       </c>
       <c r="C613" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D613" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E613" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F613" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G613" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H613" s="22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="614" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A614" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B614" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C614" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D614" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E614" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F614" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="G614" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H614" s="32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="615" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A615" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B615" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="C615" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D613" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E613" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F613" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G613" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H613" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="614" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A614" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B614" t="s">
-        <v>105</v>
-      </c>
-      <c r="C614" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D614" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E614" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F614" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G614" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H614" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="615" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A615" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B615" t="s">
-        <v>105</v>
-      </c>
-      <c r="C615" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D615" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E615" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F615" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G615" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H615" s="22" t="s">
+      <c r="D615" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E615" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="F615" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G615" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H615" s="29" t="s">
         <v>15</v>
       </c>
     </row>
@@ -17753,14 +17752,14 @@
       <c r="A616" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B616" t="s">
-        <v>106</v>
+      <c r="B616" s="17" t="s">
+        <v>104</v>
       </c>
       <c r="C616" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D616" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E616" s="22" t="s">
         <v>15</v>
@@ -17779,14 +17778,14 @@
       <c r="A617" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B617" t="s">
-        <v>106</v>
+      <c r="B617" s="17" t="s">
+        <v>104</v>
       </c>
       <c r="C617" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D617" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E617" s="22" t="s">
         <v>15</v>
@@ -17805,14 +17804,14 @@
       <c r="A618" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B618" t="s">
-        <v>106</v>
+      <c r="B618" s="17" t="s">
+        <v>104</v>
       </c>
       <c r="C618" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D618" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E618" s="22" t="s">
         <v>15</v>
@@ -17831,14 +17830,14 @@
       <c r="A619" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B619" t="s">
-        <v>106</v>
+      <c r="B619" s="17" t="s">
+        <v>104</v>
       </c>
       <c r="C619" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D619" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E619" s="22" t="s">
         <v>15</v>
@@ -17857,14 +17856,14 @@
       <c r="A620" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B620" t="s">
-        <v>106</v>
+      <c r="B620" s="17" t="s">
+        <v>104</v>
       </c>
       <c r="C620" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D620" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E620" s="22" t="s">
         <v>15</v>
@@ -17883,14 +17882,14 @@
       <c r="A621" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B621" t="s">
-        <v>106</v>
+      <c r="B621" s="17" t="s">
+        <v>104</v>
       </c>
       <c r="C621" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D621" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E621" s="22" t="s">
         <v>15</v>
@@ -17909,14 +17908,14 @@
       <c r="A622" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B622" t="s">
-        <v>106</v>
+      <c r="B622" s="17" t="s">
+        <v>104</v>
       </c>
       <c r="C622" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D622" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E622" s="22" t="s">
         <v>15</v>
@@ -17935,14 +17934,14 @@
       <c r="A623" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B623" t="s">
-        <v>106</v>
+      <c r="B623" s="17" t="s">
+        <v>104</v>
       </c>
       <c r="C623" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D623" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E623" s="22" t="s">
         <v>15</v>
@@ -17961,14 +17960,14 @@
       <c r="A624" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B624" t="s">
-        <v>106</v>
+      <c r="B624" s="17" t="s">
+        <v>105</v>
       </c>
       <c r="C624" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D624" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E624" s="22" t="s">
         <v>15</v>
@@ -17987,14 +17986,14 @@
       <c r="A625" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B625" t="s">
-        <v>107</v>
+      <c r="B625" s="17" t="s">
+        <v>105</v>
       </c>
       <c r="C625" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D625" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E625" s="22" t="s">
         <v>15</v>
@@ -18013,14 +18012,14 @@
       <c r="A626" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B626" t="s">
-        <v>107</v>
+      <c r="B626" s="17" t="s">
+        <v>105</v>
       </c>
       <c r="C626" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D626" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E626" s="22" t="s">
         <v>15</v>
@@ -18039,14 +18038,14 @@
       <c r="A627" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B627" t="s">
-        <v>107</v>
+      <c r="B627" s="17" t="s">
+        <v>105</v>
       </c>
       <c r="C627" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D627" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E627" s="22" t="s">
         <v>15</v>
@@ -18065,14 +18064,14 @@
       <c r="A628" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B628" t="s">
-        <v>107</v>
+      <c r="B628" s="17" t="s">
+        <v>105</v>
       </c>
       <c r="C628" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D628" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E628" s="22" t="s">
         <v>15</v>
@@ -18091,14 +18090,14 @@
       <c r="A629" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B629" t="s">
-        <v>107</v>
+      <c r="B629" s="17" t="s">
+        <v>105</v>
       </c>
       <c r="C629" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D629" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E629" s="22" t="s">
         <v>15</v>
@@ -18117,14 +18116,14 @@
       <c r="A630" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B630" t="s">
-        <v>107</v>
+      <c r="B630" s="17" t="s">
+        <v>105</v>
       </c>
       <c r="C630" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D630" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E630" s="22" t="s">
         <v>15</v>
@@ -18143,14 +18142,14 @@
       <c r="A631" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B631" t="s">
-        <v>107</v>
+      <c r="B631" s="17" t="s">
+        <v>105</v>
       </c>
       <c r="C631" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D631" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E631" s="22" t="s">
         <v>15</v>
@@ -18169,14 +18168,14 @@
       <c r="A632" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B632" t="s">
-        <v>108</v>
+      <c r="B632" s="17" t="s">
+        <v>105</v>
       </c>
       <c r="C632" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D632" s="20" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E632" s="22" t="s">
         <v>15</v>
@@ -18195,14 +18194,14 @@
       <c r="A633" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B633" t="s">
-        <v>108</v>
+      <c r="B633" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C633" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D633" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E633" s="22" t="s">
         <v>15</v>
@@ -18221,14 +18220,14 @@
       <c r="A634" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B634" t="s">
-        <v>108</v>
+      <c r="B634" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C634" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D634" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E634" s="22" t="s">
         <v>15</v>
@@ -18247,14 +18246,14 @@
       <c r="A635" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B635" t="s">
-        <v>108</v>
+      <c r="B635" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C635" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D635" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E635" s="22" t="s">
         <v>15</v>
@@ -18273,14 +18272,14 @@
       <c r="A636" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B636" t="s">
-        <v>108</v>
+      <c r="B636" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C636" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D636" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E636" s="22" t="s">
         <v>15</v>
@@ -18299,14 +18298,14 @@
       <c r="A637" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B637" t="s">
-        <v>108</v>
+      <c r="B637" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C637" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D637" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E637" s="22" t="s">
         <v>15</v>
@@ -18325,14 +18324,14 @@
       <c r="A638" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B638" t="s">
-        <v>108</v>
+      <c r="B638" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C638" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D638" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E638" s="22" t="s">
         <v>15</v>
@@ -18351,14 +18350,14 @@
       <c r="A639" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B639" t="s">
-        <v>108</v>
+      <c r="B639" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C639" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D639" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E639" s="22" t="s">
         <v>15</v>
@@ -18377,14 +18376,14 @@
       <c r="A640" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B640" t="s">
-        <v>108</v>
+      <c r="B640" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C640" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D640" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E640" s="22" t="s">
         <v>15</v>
@@ -18403,14 +18402,14 @@
       <c r="A641" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B641" t="s">
-        <v>109</v>
+      <c r="B641" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="C641" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D641" s="20" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E641" s="22" t="s">
         <v>15</v>
@@ -18429,14 +18428,14 @@
       <c r="A642" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B642" t="s">
-        <v>109</v>
+      <c r="B642" s="17" t="s">
+        <v>107</v>
       </c>
       <c r="C642" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D642" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E642" s="22" t="s">
         <v>15</v>
@@ -18455,14 +18454,14 @@
       <c r="A643" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B643" t="s">
-        <v>109</v>
+      <c r="B643" s="17" t="s">
+        <v>107</v>
       </c>
       <c r="C643" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D643" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E643" s="22" t="s">
         <v>15</v>
@@ -18481,14 +18480,14 @@
       <c r="A644" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B644" t="s">
-        <v>109</v>
+      <c r="B644" s="17" t="s">
+        <v>107</v>
       </c>
       <c r="C644" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D644" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E644" s="22" t="s">
         <v>15</v>
@@ -18507,14 +18506,14 @@
       <c r="A645" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B645" t="s">
-        <v>109</v>
+      <c r="B645" s="17" t="s">
+        <v>107</v>
       </c>
       <c r="C645" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D645" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E645" s="22" t="s">
         <v>15</v>
@@ -18533,14 +18532,14 @@
       <c r="A646" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B646" t="s">
-        <v>109</v>
+      <c r="B646" s="17" t="s">
+        <v>107</v>
       </c>
       <c r="C646" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D646" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E646" s="22" t="s">
         <v>15</v>
@@ -18559,14 +18558,14 @@
       <c r="A647" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B647" t="s">
-        <v>109</v>
+      <c r="B647" s="17" t="s">
+        <v>107</v>
       </c>
       <c r="C647" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D647" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E647" s="22" t="s">
         <v>15</v>
@@ -18585,14 +18584,14 @@
       <c r="A648" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B648" t="s">
-        <v>109</v>
+      <c r="B648" s="17" t="s">
+        <v>107</v>
       </c>
       <c r="C648" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D648" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E648" s="22" t="s">
         <v>15</v>
@@ -18611,14 +18610,14 @@
       <c r="A649" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B649" t="s">
-        <v>109</v>
+      <c r="B649" s="17" t="s">
+        <v>107</v>
       </c>
       <c r="C649" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D649" s="20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E649" s="22" t="s">
         <v>15</v>
@@ -18637,66 +18636,66 @@
       <c r="A650" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B650" t="s">
-        <v>110</v>
+      <c r="B650" s="17" t="s">
+        <v>107</v>
       </c>
       <c r="C650" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D650" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E650" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F650" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G650" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H650" s="22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="651" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A651" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B651" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C651" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D651" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E651" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F651" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="G651" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H651" s="32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="652" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A652" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B652" t="s">
+        <v>108</v>
+      </c>
+      <c r="C652" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D650" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E650" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F650" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G650" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H650" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="651" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A651" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B651" t="s">
-        <v>110</v>
-      </c>
-      <c r="C651" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D651" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E651" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F651" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G651" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H651" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="652" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A652" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B652" t="s">
-        <v>110</v>
-      </c>
-      <c r="C652" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D652" s="20" t="s">
-        <v>28</v>
+      <c r="D652" s="19" t="s">
+        <v>13</v>
       </c>
       <c r="E652" s="22" t="s">
         <v>15</v>
@@ -18716,13 +18715,13 @@
         <v>87</v>
       </c>
       <c r="B653" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C653" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D653" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E653" s="22" t="s">
         <v>15</v>
@@ -18742,13 +18741,13 @@
         <v>87</v>
       </c>
       <c r="B654" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C654" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D654" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E654" s="22" t="s">
         <v>15</v>
@@ -18768,13 +18767,13 @@
         <v>87</v>
       </c>
       <c r="B655" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C655" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D655" s="20" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E655" s="22" t="s">
         <v>15</v>
@@ -18794,13 +18793,13 @@
         <v>87</v>
       </c>
       <c r="B656" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C656" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D656" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E656" s="22" t="s">
         <v>15</v>
@@ -18820,13 +18819,13 @@
         <v>87</v>
       </c>
       <c r="B657" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C657" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D657" s="20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E657" s="22" t="s">
         <v>15</v>
@@ -41264,7 +41263,7 @@
           <x14:formula1>
             <xm:f>'Affix Registry'!$A$5:$A$45</xm:f>
           </x14:formula1>
-          <xm:sqref>G24:H32 F25:F32 E20 E17 E13 E10 E237:G239 H236:H239 E29:E70 F33:H70 F289:H289 E240:H288 F1074:H1075 E71:H117 F118:H119 E120:H154 E156:H235 F155:H155 E290:H1073 E1076:H1414</xm:sqref>
+          <xm:sqref>G24:H32 F25:F32 E20 E17 E13 E10 E237:G239 H236:H239 E29:E70 F33:H70 F289:H289 E240:H288 F1074:H1075 E71:H117 F118:H119 E120:H154 E156:H235 F155:H155 E1076:H1414 E290:H1073</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7AE3FD4B-CA8F-4277-A9AA-17A87684422A}">
           <x14:formula1>

--- a/Class_Gear_and_Gem_Database.xlsx
+++ b/Class_Gear_and_Gem_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orien\Desktop\mistfall calc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBAB0F1-93DD-4806-A416-0031FA731D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C50F33-0CBA-447C-89B5-665ECBC5F5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="315" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gear Database" sheetId="1" r:id="rId1"/>
@@ -11123,7 +11123,7 @@
         <v>61</v>
       </c>
       <c r="B361" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C361" s="4" t="s">
         <v>42</v>
@@ -11148,8 +11148,8 @@
       <c r="A362" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B362" s="18" t="s">
-        <v>74</v>
+      <c r="B362" s="17" t="s">
+        <v>73</v>
       </c>
       <c r="C362" s="15" t="s">
         <v>42</v>

--- a/Class_Gear_and_Gem_Database.xlsx
+++ b/Class_Gear_and_Gem_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orien\Desktop\mistfall calc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C50F33-0CBA-447C-89B5-665ECBC5F5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD169E3-4EC3-4CB8-A4D1-D7F739F0DB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2376,7 +2376,7 @@
         <v>20</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>15</v>

--- a/Class_Gear_and_Gem_Database.xlsx
+++ b/Class_Gear_and_Gem_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orien\Desktop\mistfall calc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD169E3-4EC3-4CB8-A4D1-D7F739F0DB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8807549-8E05-4B4E-BAE0-4BDBBD56A970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9600" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gear Database" sheetId="1" r:id="rId1"/>
@@ -9237,7 +9237,7 @@
         <v>343</v>
       </c>
       <c r="F288" s="27" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G288" s="27" t="s">
         <v>26</v>

--- a/Class_Gear_and_Gem_Database.xlsx
+++ b/Class_Gear_and_Gem_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orien\Desktop\mistfall calc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8807549-8E05-4B4E-BAE0-4BDBBD56A970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E52F21-A837-4946-A547-0FCED580FCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9600" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
